--- a/Simulacao_Taxa_Homicidios_UF_2010_2024.xlsx
+++ b/Simulacao_Taxa_Homicidios_UF_2010_2024.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/904989930feeffce/Documentos/GitHub/Dados-Simulados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_FFC65FC06391EFB1F426DB51FDAC5A7960B580E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA5BF9C-7361-4868-AD7C-74F145B562B8}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="17140" windowHeight="9910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -112,8 +118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,13 +182,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -220,7 +234,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -254,6 +268,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -288,9 +303,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,11 +479,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E391"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -501,7 +522,7 @@
         <v>5928</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -518,7 +539,7 @@
         <v>14809</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -535,7 +556,7 @@
         <v>3848</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -552,7 +573,7 @@
         <v>18305</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -569,7 +590,7 @@
         <v>6049</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -586,7 +607,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -603,7 +624,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -614,13 +635,13 @@
         <v>43234783</v>
       </c>
       <c r="D9">
-        <v>17.74</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="E9">
         <v>7669</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -637,7 +658,7 @@
         <v>22790</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -654,7 +675,7 @@
         <v>9234</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -671,7 +692,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -688,7 +709,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -705,7 +726,7 @@
         <v>6377</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -722,7 +743,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -739,7 +760,7 @@
         <v>4092</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -756,7 +777,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -773,7 +794,7 @@
         <v>4749</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -790,7 +811,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -807,7 +828,7 @@
         <v>21234</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -824,7 +845,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -841,7 +862,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -858,7 +879,7 @@
         <v>4852</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -875,7 +896,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -892,7 +913,7 @@
         <v>5633</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -909,7 +930,7 @@
         <v>7342</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -920,13 +941,13 @@
         <v>22835235</v>
       </c>
       <c r="D27">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="E27">
         <v>8266</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -943,7 +964,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -960,7 +981,7 @@
         <v>5046</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -977,7 +998,7 @@
         <v>6042</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -988,13 +1009,13 @@
         <v>34619117</v>
       </c>
       <c r="D31">
-        <v>40.87</v>
+        <v>40.869999999999997</v>
       </c>
       <c r="E31">
         <v>14148</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1005,13 +1026,13 @@
         <v>35061725</v>
       </c>
       <c r="D32">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="E32">
         <v>5876</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1028,7 +1049,7 @@
         <v>6150</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1039,13 +1060,13 @@
         <v>37549111</v>
       </c>
       <c r="D34">
-        <v>37.38</v>
+        <v>37.380000000000003</v>
       </c>
       <c r="E34">
         <v>14035</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1062,7 +1083,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1079,7 +1100,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1090,13 +1111,13 @@
         <v>11288678</v>
       </c>
       <c r="D37">
-        <v>9.470000000000001</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="E37">
         <v>1069</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1113,7 +1134,7 @@
         <v>5709</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1124,13 +1145,13 @@
         <v>24217335</v>
       </c>
       <c r="D39">
-        <v>16.92</v>
+        <v>16.920000000000002</v>
       </c>
       <c r="E39">
         <v>4097</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1147,7 +1168,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1164,7 +1185,7 @@
         <v>18516</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -1181,7 +1202,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -1198,7 +1219,7 @@
         <v>7526</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1215,7 +1236,7 @@
         <v>16478</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1232,7 +1253,7 @@
         <v>5261</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1249,7 +1270,7 @@
         <v>4506</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -1266,7 +1287,7 @@
         <v>19302</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +1304,7 @@
         <v>8956</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1300,7 +1321,7 @@
         <v>3699</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -1317,7 +1338,7 @@
         <v>6354</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1355,7 @@
         <v>9068</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -1351,7 +1372,7 @@
         <v>8132</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1368,7 +1389,7 @@
         <v>9030</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1385,7 +1406,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1402,7 +1423,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -1419,7 +1440,7 @@
         <v>16998</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1436,7 +1457,7 @@
         <v>8902</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -1453,7 +1474,7 @@
         <v>8528</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1491,7 @@
         <v>16323</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1508,7 @@
         <v>13835</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1525,7 @@
         <v>4892</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -1521,7 +1542,7 @@
         <v>21162</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -1538,7 +1559,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -1555,7 +1576,7 @@
         <v>23718</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -1572,7 +1593,7 @@
         <v>20642</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -1589,7 +1610,7 @@
         <v>5864</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -1606,7 +1627,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -1623,7 +1644,7 @@
         <v>4634</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -1640,7 +1661,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -1657,7 +1678,7 @@
         <v>3419</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -1674,7 +1695,7 @@
         <v>8524</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -1691,7 +1712,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -1702,13 +1723,13 @@
         <v>16766473</v>
       </c>
       <c r="D73">
-        <v>18.33</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="E73">
         <v>3073</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -1725,7 +1746,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -1742,7 +1763,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -1753,13 +1774,13 @@
         <v>18773392</v>
       </c>
       <c r="D76">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="E76">
         <v>6782</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -1770,13 +1791,13 @@
         <v>17316569</v>
       </c>
       <c r="D77">
-        <v>8.890000000000001</v>
+        <v>8.89</v>
       </c>
       <c r="E77">
         <v>1539</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -1793,7 +1814,7 @@
         <v>5117</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -1810,7 +1831,7 @@
         <v>18609</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -1827,7 +1848,7 @@
         <v>3669</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -1844,7 +1865,7 @@
         <v>3544</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -1861,7 +1882,7 @@
         <v>4991</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -1878,7 +1899,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -1895,7 +1916,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -1912,7 +1933,7 @@
         <v>16546</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -1929,7 +1950,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -1946,7 +1967,7 @@
         <v>8396</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -1963,7 +1984,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -1980,7 +2001,7 @@
         <v>4398</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -1991,13 +2012,13 @@
         <v>41157662</v>
       </c>
       <c r="D90">
-        <v>19.26</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="E90">
         <v>7926</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -2014,7 +2035,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -2031,7 +2052,7 @@
         <v>15945</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -2048,7 +2069,7 @@
         <v>5030</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -2065,7 +2086,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -2082,7 +2103,7 @@
         <v>5014</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -2093,13 +2114,13 @@
         <v>41410172</v>
       </c>
       <c r="D96">
-        <v>16.19</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="E96">
         <v>6704</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -2116,7 +2137,7 @@
         <v>14088</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -2133,7 +2154,7 @@
         <v>6367</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2144,13 +2165,13 @@
         <v>33767858</v>
       </c>
       <c r="D99">
-        <v>35.73</v>
+        <v>35.729999999999997</v>
       </c>
       <c r="E99">
         <v>12065</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -2167,7 +2188,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -2184,7 +2205,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -2201,7 +2222,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -2218,7 +2239,7 @@
         <v>10334</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -2235,7 +2256,7 @@
         <v>4609</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -2252,7 +2273,7 @@
         <v>7770</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -2269,7 +2290,7 @@
         <v>19948</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>12</v>
       </c>
@@ -2286,7 +2307,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>12</v>
       </c>
@@ -2303,7 +2324,7 @@
         <v>19590</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>12</v>
       </c>
@@ -2320,7 +2341,7 @@
         <v>11741</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>12</v>
       </c>
@@ -2337,7 +2358,7 @@
         <v>18661</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -2354,7 +2375,7 @@
         <v>12819</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>12</v>
       </c>
@@ -2371,7 +2392,7 @@
         <v>10295</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>12</v>
       </c>
@@ -2388,7 +2409,7 @@
         <v>6114</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>12</v>
       </c>
@@ -2405,7 +2426,7 @@
         <v>3848</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -2422,7 +2443,7 @@
         <v>13230</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>12</v>
       </c>
@@ -2439,7 +2460,7 @@
         <v>5994</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>12</v>
       </c>
@@ -2456,7 +2477,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -2473,7 +2494,7 @@
         <v>13267</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -2490,7 +2511,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>12</v>
       </c>
@@ -2507,7 +2528,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>12</v>
       </c>
@@ -2524,7 +2545,7 @@
         <v>20373</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -2541,7 +2562,7 @@
         <v>7270</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -2558,7 +2579,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -2575,7 +2596,7 @@
         <v>7593</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -2592,7 +2613,7 @@
         <v>10558</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -2609,7 +2630,7 @@
         <v>12281</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -2620,13 +2641,13 @@
         <v>38356186</v>
       </c>
       <c r="D127">
-        <v>37.55</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="E127">
         <v>14402</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -2643,7 +2664,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -2660,7 +2681,7 @@
         <v>3692</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -2677,7 +2698,7 @@
         <v>6797</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -2694,7 +2715,7 @@
         <v>15721</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -2711,7 +2732,7 @@
         <v>8597</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -2722,13 +2743,13 @@
         <v>35472607</v>
       </c>
       <c r="D133">
-        <v>35.16</v>
+        <v>35.159999999999997</v>
       </c>
       <c r="E133">
         <v>12472</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -2745,7 +2766,7 @@
         <v>9323</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -2756,13 +2777,13 @@
         <v>41320227</v>
       </c>
       <c r="D135">
-        <v>34.95</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="E135">
         <v>14441</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -2779,7 +2800,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>14</v>
       </c>
@@ -2796,7 +2817,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>14</v>
       </c>
@@ -2813,7 +2834,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -2830,7 +2851,7 @@
         <v>8050</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>14</v>
       </c>
@@ -2847,7 +2868,7 @@
         <v>7666</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>14</v>
       </c>
@@ -2864,7 +2885,7 @@
         <v>6410</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>14</v>
       </c>
@@ -2881,7 +2902,7 @@
         <v>25369</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>14</v>
       </c>
@@ -2898,7 +2919,7 @@
         <v>3654</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>14</v>
       </c>
@@ -2915,7 +2936,7 @@
         <v>9058</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -2932,7 +2953,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>14</v>
       </c>
@@ -2949,7 +2970,7 @@
         <v>6543</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>14</v>
       </c>
@@ -2966,7 +2987,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>14</v>
       </c>
@@ -2983,7 +3004,7 @@
         <v>15419</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>14</v>
       </c>
@@ -2994,13 +3015,13 @@
         <v>25383825</v>
       </c>
       <c r="D149">
-        <v>9.220000000000001</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="E149">
         <v>2340</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>14</v>
       </c>
@@ -3017,7 +3038,7 @@
         <v>10429</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>14</v>
       </c>
@@ -3034,7 +3055,7 @@
         <v>4875</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -3051,7 +3072,7 @@
         <v>3859</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -3068,7 +3089,7 @@
         <v>5266</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -3085,7 +3106,7 @@
         <v>11869</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -3102,7 +3123,7 @@
         <v>7216</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -3119,7 +3140,7 @@
         <v>17404</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -3136,7 +3157,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -3147,13 +3168,13 @@
         <v>6599628</v>
       </c>
       <c r="D158">
-        <v>35.09</v>
+        <v>35.090000000000003</v>
       </c>
       <c r="E158">
         <v>2315</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -3170,7 +3191,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -3187,7 +3208,7 @@
         <v>8115</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -3204,7 +3225,7 @@
         <v>25048</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -3221,7 +3242,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -3238,7 +3259,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -3255,7 +3276,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -3272,7 +3293,7 @@
         <v>7650</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -3289,7 +3310,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -3306,7 +3327,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -3323,7 +3344,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -3340,7 +3361,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -3357,7 +3378,7 @@
         <v>4738</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -3374,7 +3395,7 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -3385,13 +3406,13 @@
         <v>21144716</v>
       </c>
       <c r="D172">
-        <v>10.12</v>
+        <v>10.119999999999999</v>
       </c>
       <c r="E172">
         <v>2139</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -3408,7 +3429,7 @@
         <v>3735</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -3425,7 +3446,7 @@
         <v>11992</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -3442,7 +3463,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -3453,13 +3474,13 @@
         <v>42665906</v>
       </c>
       <c r="D176">
-        <v>35.98</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="E176">
         <v>15351</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -3476,7 +3497,7 @@
         <v>12052</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -3493,7 +3514,7 @@
         <v>13031</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -3504,13 +3525,13 @@
         <v>42271748</v>
       </c>
       <c r="D179">
-        <v>9.710000000000001</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="E179">
         <v>4104</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -3521,13 +3542,13 @@
         <v>12302429</v>
       </c>
       <c r="D180">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="E180">
         <v>1975</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -3544,7 +3565,7 @@
         <v>20352</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>17</v>
       </c>
@@ -3561,7 +3582,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -3578,7 +3599,7 @@
         <v>12784</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -3589,13 +3610,13 @@
         <v>10600349</v>
       </c>
       <c r="D184">
-        <v>20.01</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="E184">
         <v>2121</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -3612,7 +3633,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -3629,7 +3650,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -3646,7 +3667,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -3663,7 +3684,7 @@
         <v>4045</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -3680,7 +3701,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -3697,7 +3718,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -3714,7 +3735,7 @@
         <v>14770</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -3731,7 +3752,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -3748,7 +3769,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -3765,7 +3786,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -3782,7 +3803,7 @@
         <v>3434</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -3799,7 +3820,7 @@
         <v>6126</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -3816,7 +3837,7 @@
         <v>6124</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -3833,7 +3854,7 @@
         <v>8184</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -3850,7 +3871,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -3867,7 +3888,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -3884,7 +3905,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -3901,7 +3922,7 @@
         <v>13036</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -3918,7 +3939,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -3935,7 +3956,7 @@
         <v>21028</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -3952,7 +3973,7 @@
         <v>4908</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -3969,7 +3990,7 @@
         <v>12328</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -3986,7 +4007,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -4003,7 +4024,7 @@
         <v>4506</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -4020,7 +4041,7 @@
         <v>21242</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -4037,7 +4058,7 @@
         <v>9893</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -4054,7 +4075,7 @@
         <v>5019</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>19</v>
       </c>
@@ -4071,7 +4092,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>19</v>
       </c>
@@ -4088,7 +4109,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>19</v>
       </c>
@@ -4105,7 +4126,7 @@
         <v>15452</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>19</v>
       </c>
@@ -4122,7 +4143,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>19</v>
       </c>
@@ -4139,7 +4160,7 @@
         <v>11902</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>19</v>
       </c>
@@ -4156,7 +4177,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>19</v>
       </c>
@@ -4173,7 +4194,7 @@
         <v>7895</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>19</v>
       </c>
@@ -4190,7 +4211,7 @@
         <v>9406</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>19</v>
       </c>
@@ -4207,7 +4228,7 @@
         <v>4751</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>19</v>
       </c>
@@ -4224,7 +4245,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>19</v>
       </c>
@@ -4241,7 +4262,7 @@
         <v>3285</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>19</v>
       </c>
@@ -4258,7 +4279,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>19</v>
       </c>
@@ -4275,7 +4296,7 @@
         <v>10492</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>19</v>
       </c>
@@ -4292,7 +4313,7 @@
         <v>5893</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>19</v>
       </c>
@@ -4309,7 +4330,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>20</v>
       </c>
@@ -4326,7 +4347,7 @@
         <v>9836</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>20</v>
       </c>
@@ -4343,7 +4364,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>20</v>
       </c>
@@ -4360,7 +4381,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>20</v>
       </c>
@@ -4377,7 +4398,7 @@
         <v>8437</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>20</v>
       </c>
@@ -4394,7 +4415,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>20</v>
       </c>
@@ -4411,7 +4432,7 @@
         <v>11629</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>20</v>
       </c>
@@ -4428,7 +4449,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>20</v>
       </c>
@@ -4445,7 +4466,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>20</v>
       </c>
@@ -4462,7 +4483,7 @@
         <v>17656</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>20</v>
       </c>
@@ -4479,7 +4500,7 @@
         <v>13432</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -4496,7 +4517,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>20</v>
       </c>
@@ -4513,7 +4534,7 @@
         <v>16231</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>20</v>
       </c>
@@ -4530,7 +4551,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>20</v>
       </c>
@@ -4541,13 +4562,13 @@
         <v>37842772</v>
       </c>
       <c r="D240">
-        <v>17.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="E240">
         <v>6720</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -4564,7 +4585,7 @@
         <v>19127</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>21</v>
       </c>
@@ -4581,7 +4602,7 @@
         <v>4651</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>21</v>
       </c>
@@ -4598,7 +4619,7 @@
         <v>4125</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>21</v>
       </c>
@@ -4615,7 +4636,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>21</v>
       </c>
@@ -4632,7 +4653,7 @@
         <v>18219</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>21</v>
       </c>
@@ -4649,7 +4670,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>21</v>
       </c>
@@ -4666,7 +4687,7 @@
         <v>17800</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>21</v>
       </c>
@@ -4683,7 +4704,7 @@
         <v>13538</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>21</v>
       </c>
@@ -4700,7 +4721,7 @@
         <v>10292</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>21</v>
       </c>
@@ -4717,7 +4738,7 @@
         <v>20979</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>21</v>
       </c>
@@ -4734,7 +4755,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>21</v>
       </c>
@@ -4751,7 +4772,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>21</v>
       </c>
@@ -4762,13 +4783,13 @@
         <v>10226290</v>
       </c>
       <c r="D253">
-        <v>35.8</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="E253">
         <v>3661</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>21</v>
       </c>
@@ -4779,13 +4800,13 @@
         <v>16664204</v>
       </c>
       <c r="D254">
-        <v>39.88</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="E254">
         <v>6645</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>21</v>
       </c>
@@ -4802,7 +4823,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>21</v>
       </c>
@@ -4819,7 +4840,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>22</v>
       </c>
@@ -4836,7 +4857,7 @@
         <v>9629</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>22</v>
       </c>
@@ -4853,7 +4874,7 @@
         <v>5778</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>22</v>
       </c>
@@ -4870,7 +4891,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>22</v>
       </c>
@@ -4887,7 +4908,7 @@
         <v>4073</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>22</v>
       </c>
@@ -4898,13 +4919,13 @@
         <v>9637682</v>
       </c>
       <c r="D261">
-        <v>19.92</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="E261">
         <v>1919</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>22</v>
       </c>
@@ -4921,7 +4942,7 @@
         <v>4193</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>22</v>
       </c>
@@ -4938,7 +4959,7 @@
         <v>7893</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>22</v>
       </c>
@@ -4949,13 +4970,13 @@
         <v>41057019</v>
       </c>
       <c r="D264">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="E264">
         <v>3440</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -4972,7 +4993,7 @@
         <v>22808</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>22</v>
       </c>
@@ -4989,7 +5010,7 @@
         <v>17518</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>22</v>
       </c>
@@ -5006,7 +5027,7 @@
         <v>15743</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>22</v>
       </c>
@@ -5023,7 +5044,7 @@
         <v>11315</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>22</v>
       </c>
@@ -5040,7 +5061,7 @@
         <v>8881</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>22</v>
       </c>
@@ -5051,13 +5072,13 @@
         <v>43868581</v>
       </c>
       <c r="D270">
-        <v>36.7</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="E270">
         <v>16099</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>22</v>
       </c>
@@ -5074,7 +5095,7 @@
         <v>21146</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>23</v>
       </c>
@@ -5091,7 +5112,7 @@
         <v>27961</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>23</v>
       </c>
@@ -5108,7 +5129,7 @@
         <v>7244</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>23</v>
       </c>
@@ -5125,7 +5146,7 @@
         <v>8616</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>23</v>
       </c>
@@ -5136,13 +5157,13 @@
         <v>2873139</v>
       </c>
       <c r="D275">
-        <v>38.23</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="E275">
         <v>1098</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>23</v>
       </c>
@@ -5153,13 +5174,13 @@
         <v>43301198</v>
       </c>
       <c r="D276">
-        <v>9.529999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="E276">
         <v>4126</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -5176,7 +5197,7 @@
         <v>15362</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>23</v>
       </c>
@@ -5193,7 +5214,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>23</v>
       </c>
@@ -5210,7 +5231,7 @@
         <v>18738</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>23</v>
       </c>
@@ -5227,7 +5248,7 @@
         <v>23139</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>23</v>
       </c>
@@ -5244,7 +5265,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>23</v>
       </c>
@@ -5255,13 +5276,13 @@
         <v>32862868</v>
       </c>
       <c r="D282">
-        <v>32.34</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="E282">
         <v>10627</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>23</v>
       </c>
@@ -5278,7 +5299,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>23</v>
       </c>
@@ -5295,7 +5316,7 @@
         <v>18286</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>23</v>
       </c>
@@ -5306,13 +5327,13 @@
         <v>1844027</v>
       </c>
       <c r="D285">
-        <v>18.76</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="E285">
         <v>345</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>23</v>
       </c>
@@ -5329,7 +5350,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>24</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>24</v>
       </c>
@@ -5363,7 +5384,7 @@
         <v>9994</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>24</v>
       </c>
@@ -5380,7 +5401,7 @@
         <v>4747</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>24</v>
       </c>
@@ -5397,7 +5418,7 @@
         <v>12598</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>24</v>
       </c>
@@ -5414,7 +5435,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>24</v>
       </c>
@@ -5431,7 +5452,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>24</v>
       </c>
@@ -5448,7 +5469,7 @@
         <v>18865</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>24</v>
       </c>
@@ -5459,13 +5480,13 @@
         <v>20357417</v>
       </c>
       <c r="D294">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="E294">
         <v>8116</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>24</v>
       </c>
@@ -5482,7 +5503,7 @@
         <v>17817</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>24</v>
       </c>
@@ -5499,7 +5520,7 @@
         <v>14237</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>24</v>
       </c>
@@ -5516,7 +5537,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>24</v>
       </c>
@@ -5533,7 +5554,7 @@
         <v>6695</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>24</v>
       </c>
@@ -5550,7 +5571,7 @@
         <v>5109</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>24</v>
       </c>
@@ -5567,7 +5588,7 @@
         <v>10488</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>24</v>
       </c>
@@ -5584,7 +5605,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>25</v>
       </c>
@@ -5601,7 +5622,7 @@
         <v>24613</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>25</v>
       </c>
@@ -5618,7 +5639,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>25</v>
       </c>
@@ -5635,7 +5656,7 @@
         <v>10139</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>25</v>
       </c>
@@ -5652,7 +5673,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>25</v>
       </c>
@@ -5669,7 +5690,7 @@
         <v>6416</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>25</v>
       </c>
@@ -5686,7 +5707,7 @@
         <v>19625</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>25</v>
       </c>
@@ -5703,7 +5724,7 @@
         <v>5727</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>25</v>
       </c>
@@ -5720,7 +5741,7 @@
         <v>15014</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>25</v>
       </c>
@@ -5737,7 +5758,7 @@
         <v>16412</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>25</v>
       </c>
@@ -5754,7 +5775,7 @@
         <v>5882</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>25</v>
       </c>
@@ -5771,7 +5792,7 @@
         <v>7958</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>25</v>
       </c>
@@ -5788,7 +5809,7 @@
         <v>17784</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>25</v>
       </c>
@@ -5805,7 +5826,7 @@
         <v>17630</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>25</v>
       </c>
@@ -5822,7 +5843,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>25</v>
       </c>
@@ -5839,7 +5860,7 @@
         <v>2434</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>26</v>
       </c>
@@ -5856,7 +5877,7 @@
         <v>4848</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>26</v>
       </c>
@@ -5873,7 +5894,7 @@
         <v>13293</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>26</v>
       </c>
@@ -5890,7 +5911,7 @@
         <v>24110</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>26</v>
       </c>
@@ -5907,7 +5928,7 @@
         <v>22590</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>26</v>
       </c>
@@ -5918,13 +5939,13 @@
         <v>22564334</v>
       </c>
       <c r="D321">
-        <v>33.8</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="E321">
         <v>7626</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>26</v>
       </c>
@@ -5941,7 +5962,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>26</v>
       </c>
@@ -5958,7 +5979,7 @@
         <v>18325</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>26</v>
       </c>
@@ -5975,7 +5996,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>26</v>
       </c>
@@ -5992,7 +6013,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>26</v>
       </c>
@@ -6009,7 +6030,7 @@
         <v>12767</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>26</v>
       </c>
@@ -6026,7 +6047,7 @@
         <v>2802</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>26</v>
       </c>
@@ -6043,7 +6064,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>26</v>
       </c>
@@ -6060,7 +6081,7 @@
         <v>5645</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>26</v>
       </c>
@@ -6077,7 +6098,7 @@
         <v>13212</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>26</v>
       </c>
@@ -6094,7 +6115,7 @@
         <v>10988</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>27</v>
       </c>
@@ -6111,7 +6132,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>27</v>
       </c>
@@ -6122,13 +6143,13 @@
         <v>35903828</v>
       </c>
       <c r="D333">
-        <v>32.55</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="E333">
         <v>11686</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>27</v>
       </c>
@@ -6145,7 +6166,7 @@
         <v>6794</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -6162,7 +6183,7 @@
         <v>10872</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -6179,7 +6200,7 @@
         <v>6710</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -6196,7 +6217,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>27</v>
       </c>
@@ -6207,13 +6228,13 @@
         <v>42055914</v>
       </c>
       <c r="D338">
-        <v>40.09</v>
+        <v>40.090000000000003</v>
       </c>
       <c r="E338">
         <v>16860</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>27</v>
       </c>
@@ -6230,7 +6251,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>27</v>
       </c>
@@ -6247,7 +6268,7 @@
         <v>6187</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>27</v>
       </c>
@@ -6264,7 +6285,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>27</v>
       </c>
@@ -6281,7 +6302,7 @@
         <v>11048</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>27</v>
       </c>
@@ -6298,7 +6319,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>27</v>
       </c>
@@ -6315,7 +6336,7 @@
         <v>7446</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>27</v>
       </c>
@@ -6332,7 +6353,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>27</v>
       </c>
@@ -6349,7 +6370,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>28</v>
       </c>
@@ -6366,7 +6387,7 @@
         <v>4084</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>28</v>
       </c>
@@ -6383,7 +6404,7 @@
         <v>4198</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>28</v>
       </c>
@@ -6400,7 +6421,7 @@
         <v>4076</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>28</v>
       </c>
@@ -6417,7 +6438,7 @@
         <v>9802</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>28</v>
       </c>
@@ -6434,7 +6455,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>28</v>
       </c>
@@ -6445,13 +6466,13 @@
         <v>1722869</v>
       </c>
       <c r="D352">
-        <v>33.87</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="E352">
         <v>583</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>28</v>
       </c>
@@ -6468,7 +6489,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>28</v>
       </c>
@@ -6485,7 +6506,7 @@
         <v>7016</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>28</v>
       </c>
@@ -6502,7 +6523,7 @@
         <v>8764</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>28</v>
       </c>
@@ -6519,7 +6540,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>28</v>
       </c>
@@ -6536,7 +6557,7 @@
         <v>4376</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>28</v>
       </c>
@@ -6547,13 +6568,13 @@
         <v>9806167</v>
       </c>
       <c r="D358">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="E358">
         <v>3647</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>28</v>
       </c>
@@ -6570,7 +6591,7 @@
         <v>13164</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>28</v>
       </c>
@@ -6587,7 +6608,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>28</v>
       </c>
@@ -6604,7 +6625,7 @@
         <v>7806</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>29</v>
       </c>
@@ -6621,7 +6642,7 @@
         <v>4901</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>29</v>
       </c>
@@ -6638,7 +6659,7 @@
         <v>9645</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>29</v>
       </c>
@@ -6655,7 +6676,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>29</v>
       </c>
@@ -6672,7 +6693,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>29</v>
       </c>
@@ -6689,7 +6710,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>29</v>
       </c>
@@ -6706,7 +6727,7 @@
         <v>4624</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>29</v>
       </c>
@@ -6723,7 +6744,7 @@
         <v>9649</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>29</v>
       </c>
@@ -6734,13 +6755,13 @@
         <v>36247046</v>
       </c>
       <c r="D369">
-        <v>38.84</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="E369">
         <v>14078</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>29</v>
       </c>
@@ -6757,7 +6778,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>29</v>
       </c>
@@ -6774,7 +6795,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>29</v>
       </c>
@@ -6791,7 +6812,7 @@
         <v>15793</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>29</v>
       </c>
@@ -6808,7 +6829,7 @@
         <v>16814</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>29</v>
       </c>
@@ -6819,13 +6840,13 @@
         <v>11011829</v>
       </c>
       <c r="D374">
-        <v>40.05</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="E374">
         <v>4410</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>29</v>
       </c>
@@ -6842,7 +6863,7 @@
         <v>14725</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>29</v>
       </c>
@@ -6859,7 +6880,7 @@
         <v>3578</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>30</v>
       </c>
@@ -6876,7 +6897,7 @@
         <v>11240</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>30</v>
       </c>
@@ -6893,7 +6914,7 @@
         <v>6220</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>30</v>
       </c>
@@ -6910,7 +6931,7 @@
         <v>17971</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>30</v>
       </c>
@@ -6927,7 +6948,7 @@
         <v>2555</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>30</v>
       </c>
@@ -6944,7 +6965,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>30</v>
       </c>
@@ -6961,7 +6982,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>30</v>
       </c>
@@ -6978,7 +6999,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>30</v>
       </c>
@@ -6995,7 +7016,7 @@
         <v>6211</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>30</v>
       </c>
@@ -7012,7 +7033,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>30</v>
       </c>
@@ -7029,7 +7050,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>30</v>
       </c>
@@ -7046,7 +7067,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>30</v>
       </c>
@@ -7063,7 +7084,7 @@
         <v>3537</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>30</v>
       </c>
@@ -7080,7 +7101,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>30</v>
       </c>
@@ -7097,7 +7118,7 @@
         <v>13967</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>30</v>
       </c>

--- a/Simulacao_Taxa_Homicidios_UF_2010_2024.xlsx
+++ b/Simulacao_Taxa_Homicidios_UF_2010_2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/904989930feeffce/Documentos/GitHub/Dados-Simulados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_FFC65FC06391EFB1F426DB51FDAC5A7960B580E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA5BF9C-7361-4868-AD7C-74F145B562B8}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_FFC65FC06391EFB1F426DB51FDAC5A7960B580E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48451ED0-06C2-4059-BFC5-1169D63E2A3C}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="1060" windowWidth="17140" windowHeight="9910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="30">
   <si>
     <t>UF</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>População Estimada</t>
-  </si>
-  <si>
-    <t>Taxa de Homicídios (por 100 mil)</t>
   </si>
   <si>
     <t>Número Estimado de Homicídios</t>
@@ -191,6 +188,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,15 +481,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:D391"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,13 +501,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
       </c>
       <c r="B2">
         <v>2010</v>
@@ -516,15 +513,12 @@
         <v>21581788</v>
       </c>
       <c r="D2">
-        <v>27.47</v>
-      </c>
-      <c r="E2">
         <v>5928</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2011</v>
@@ -533,15 +527,12 @@
         <v>36288921</v>
       </c>
       <c r="D3">
-        <v>40.81</v>
-      </c>
-      <c r="E3">
         <v>14809</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>2012</v>
@@ -550,15 +541,12 @@
         <v>26801898</v>
       </c>
       <c r="D4">
-        <v>14.36</v>
-      </c>
-      <c r="E4">
         <v>3848</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>2013</v>
@@ -567,15 +555,12 @@
         <v>32132483</v>
       </c>
       <c r="D5">
-        <v>56.97</v>
-      </c>
-      <c r="E5">
         <v>18305</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>2014</v>
@@ -584,15 +569,12 @@
         <v>44581282</v>
       </c>
       <c r="D6">
-        <v>13.57</v>
-      </c>
-      <c r="E6">
         <v>6049</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>2015</v>
@@ -601,15 +583,12 @@
         <v>5481505</v>
       </c>
       <c r="D7">
-        <v>6.24</v>
-      </c>
-      <c r="E7">
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>2016</v>
@@ -618,15 +597,12 @@
         <v>5021373</v>
       </c>
       <c r="D8">
-        <v>48.32</v>
-      </c>
-      <c r="E8">
         <v>2426</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>2017</v>
@@ -635,15 +611,12 @@
         <v>43234783</v>
       </c>
       <c r="D9">
-        <v>17.739999999999998</v>
-      </c>
-      <c r="E9">
         <v>7669</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>2018</v>
@@ -652,15 +625,12 @@
         <v>35317184</v>
       </c>
       <c r="D10">
-        <v>64.53</v>
-      </c>
-      <c r="E10">
         <v>22790</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>2019</v>
@@ -669,15 +639,12 @@
         <v>39719221</v>
       </c>
       <c r="D11">
-        <v>23.25</v>
-      </c>
-      <c r="E11">
         <v>9234</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12">
         <v>2020</v>
@@ -686,15 +653,12 @@
         <v>32443512</v>
       </c>
       <c r="D12">
-        <v>5.42</v>
-      </c>
-      <c r="E12">
         <v>1758</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>2021</v>
@@ -703,15 +667,12 @@
         <v>11142490</v>
       </c>
       <c r="D13">
-        <v>22.47</v>
-      </c>
-      <c r="E13">
         <v>2503</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>2022</v>
@@ -720,15 +681,12 @@
         <v>21998555</v>
       </c>
       <c r="D14">
-        <v>28.99</v>
-      </c>
-      <c r="E14">
         <v>6377</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15">
         <v>2023</v>
@@ -737,15 +695,12 @@
         <v>13148637</v>
       </c>
       <c r="D15">
-        <v>26.98</v>
-      </c>
-      <c r="E15">
         <v>3547</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16">
         <v>2024</v>
@@ -754,15 +709,12 @@
         <v>39202013</v>
       </c>
       <c r="D16">
-        <v>10.44</v>
-      </c>
-      <c r="E16">
         <v>4092</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17">
         <v>2010</v>
@@ -771,15 +723,12 @@
         <v>2928388</v>
       </c>
       <c r="D17">
-        <v>16.98</v>
-      </c>
-      <c r="E17">
         <v>497</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18">
         <v>2011</v>
@@ -788,15 +737,12 @@
         <v>11459014</v>
       </c>
       <c r="D18">
-        <v>41.45</v>
-      </c>
-      <c r="E18">
         <v>4749</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>2012</v>
@@ -805,15 +751,12 @@
         <v>20693880</v>
       </c>
       <c r="D19">
-        <v>5.8</v>
-      </c>
-      <c r="E19">
         <v>1200</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>2013</v>
@@ -822,15 +765,12 @@
         <v>33737768</v>
       </c>
       <c r="D20">
-        <v>62.94</v>
-      </c>
-      <c r="E20">
         <v>21234</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>2014</v>
@@ -839,15 +779,12 @@
         <v>29063547</v>
       </c>
       <c r="D21">
-        <v>5.96</v>
-      </c>
-      <c r="E21">
         <v>1732</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22">
         <v>2015</v>
@@ -856,15 +793,12 @@
         <v>3169995</v>
       </c>
       <c r="D22">
-        <v>31.41</v>
-      </c>
-      <c r="E22">
         <v>995</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23">
         <v>2016</v>
@@ -873,15 +807,12 @@
         <v>13979854</v>
       </c>
       <c r="D23">
-        <v>34.71</v>
-      </c>
-      <c r="E23">
         <v>4852</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24">
         <v>2017</v>
@@ -890,15 +821,12 @@
         <v>2370928</v>
       </c>
       <c r="D24">
-        <v>15.4</v>
-      </c>
-      <c r="E24">
         <v>365</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25">
         <v>2018</v>
@@ -907,15 +835,12 @@
         <v>27439239</v>
       </c>
       <c r="D25">
-        <v>20.53</v>
-      </c>
-      <c r="E25">
         <v>5633</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26">
         <v>2019</v>
@@ -924,15 +849,12 @@
         <v>14591261</v>
       </c>
       <c r="D26">
-        <v>50.32</v>
-      </c>
-      <c r="E26">
         <v>7342</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>2020</v>
@@ -941,15 +863,12 @@
         <v>22835235</v>
       </c>
       <c r="D27">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="E27">
         <v>8266</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>2021</v>
@@ -958,15 +877,12 @@
         <v>4084702</v>
       </c>
       <c r="D28">
-        <v>16.09</v>
-      </c>
-      <c r="E28">
         <v>657</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>2022</v>
@@ -975,15 +891,12 @@
         <v>9085377</v>
       </c>
       <c r="D29">
-        <v>55.54</v>
-      </c>
-      <c r="E29">
         <v>5046</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30">
         <v>2023</v>
@@ -992,15 +905,12 @@
         <v>21046531</v>
       </c>
       <c r="D30">
-        <v>28.71</v>
-      </c>
-      <c r="E30">
         <v>6042</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>2024</v>
@@ -1009,15 +919,12 @@
         <v>34619117</v>
       </c>
       <c r="D31">
-        <v>40.869999999999997</v>
-      </c>
-      <c r="E31">
         <v>14148</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>2010</v>
@@ -1026,15 +933,12 @@
         <v>35061725</v>
       </c>
       <c r="D32">
-        <v>16.760000000000002</v>
-      </c>
-      <c r="E32">
         <v>5876</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33">
         <v>2011</v>
@@ -1043,15 +947,12 @@
         <v>25084529</v>
       </c>
       <c r="D33">
-        <v>24.52</v>
-      </c>
-      <c r="E33">
         <v>6150</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34">
         <v>2012</v>
@@ -1060,15 +961,12 @@
         <v>37549111</v>
       </c>
       <c r="D34">
-        <v>37.380000000000003</v>
-      </c>
-      <c r="E34">
         <v>14035</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35">
         <v>2013</v>
@@ -1077,15 +975,12 @@
         <v>1785160</v>
       </c>
       <c r="D35">
-        <v>26.41</v>
-      </c>
-      <c r="E35">
         <v>471</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>2014</v>
@@ -1094,15 +989,12 @@
         <v>39227468</v>
       </c>
       <c r="D36">
-        <v>22.78</v>
-      </c>
-      <c r="E36">
         <v>8936</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>2015</v>
@@ -1111,15 +1003,12 @@
         <v>11288678</v>
       </c>
       <c r="D37">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="E37">
         <v>1069</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38">
         <v>2016</v>
@@ -1128,15 +1017,12 @@
         <v>18781600</v>
       </c>
       <c r="D38">
-        <v>30.4</v>
-      </c>
-      <c r="E38">
         <v>5709</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39">
         <v>2017</v>
@@ -1145,15 +1031,12 @@
         <v>24217335</v>
       </c>
       <c r="D39">
-        <v>16.920000000000002</v>
-      </c>
-      <c r="E39">
         <v>4097</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>2018</v>
@@ -1162,15 +1045,12 @@
         <v>16530288</v>
       </c>
       <c r="D40">
-        <v>5.84</v>
-      </c>
-      <c r="E40">
         <v>965</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B41">
         <v>2019</v>
@@ -1179,15 +1059,12 @@
         <v>38834882</v>
       </c>
       <c r="D41">
-        <v>47.68</v>
-      </c>
-      <c r="E41">
         <v>18516</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42">
         <v>2020</v>
@@ -1196,15 +1073,12 @@
         <v>19509001</v>
       </c>
       <c r="D42">
-        <v>51.28</v>
-      </c>
-      <c r="E42">
         <v>10004</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43">
         <v>2021</v>
@@ -1213,15 +1087,12 @@
         <v>28391752</v>
       </c>
       <c r="D43">
-        <v>26.51</v>
-      </c>
-      <c r="E43">
         <v>7526</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44">
         <v>2022</v>
@@ -1230,15 +1101,12 @@
         <v>27509224</v>
       </c>
       <c r="D44">
-        <v>59.9</v>
-      </c>
-      <c r="E44">
         <v>16478</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45">
         <v>2023</v>
@@ -1247,15 +1115,12 @@
         <v>12410049</v>
       </c>
       <c r="D45">
-        <v>42.4</v>
-      </c>
-      <c r="E45">
         <v>5261</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46">
         <v>2024</v>
@@ -1264,15 +1129,12 @@
         <v>42042436</v>
       </c>
       <c r="D46">
-        <v>10.72</v>
-      </c>
-      <c r="E46">
         <v>4506</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B47">
         <v>2010</v>
@@ -1281,15 +1143,12 @@
         <v>39570421</v>
       </c>
       <c r="D47">
-        <v>48.78</v>
-      </c>
-      <c r="E47">
         <v>19302</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48">
         <v>2011</v>
@@ -1298,15 +1157,12 @@
         <v>15381728</v>
       </c>
       <c r="D48">
-        <v>58.23</v>
-      </c>
-      <c r="E48">
         <v>8956</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49">
         <v>2012</v>
@@ -1315,15 +1171,12 @@
         <v>13222094</v>
       </c>
       <c r="D49">
-        <v>27.98</v>
-      </c>
-      <c r="E49">
         <v>3699</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50">
         <v>2013</v>
@@ -1332,15 +1185,12 @@
         <v>13296932</v>
       </c>
       <c r="D50">
-        <v>47.79</v>
-      </c>
-      <c r="E50">
         <v>6354</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51">
         <v>2014</v>
@@ -1349,15 +1199,12 @@
         <v>23444510</v>
       </c>
       <c r="D51">
-        <v>38.68</v>
-      </c>
-      <c r="E51">
         <v>9068</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52">
         <v>2015</v>
@@ -1366,15 +1213,12 @@
         <v>39943226</v>
       </c>
       <c r="D52">
-        <v>20.36</v>
-      </c>
-      <c r="E52">
         <v>8132</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B53">
         <v>2016</v>
@@ -1383,15 +1227,12 @@
         <v>24835374</v>
       </c>
       <c r="D53">
-        <v>36.36</v>
-      </c>
-      <c r="E53">
         <v>9030</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B54">
         <v>2017</v>
@@ -1400,15 +1241,12 @@
         <v>8387739</v>
       </c>
       <c r="D54">
-        <v>11.65</v>
-      </c>
-      <c r="E54">
         <v>977</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55">
         <v>2018</v>
@@ -1417,15 +1255,12 @@
         <v>1269598</v>
       </c>
       <c r="D55">
-        <v>11.47</v>
-      </c>
-      <c r="E55">
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56">
         <v>2019</v>
@@ -1434,15 +1269,12 @@
         <v>28933648</v>
       </c>
       <c r="D56">
-        <v>58.75</v>
-      </c>
-      <c r="E56">
         <v>16998</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57">
         <v>2020</v>
@@ -1451,15 +1283,12 @@
         <v>37310847</v>
       </c>
       <c r="D57">
-        <v>23.86</v>
-      </c>
-      <c r="E57">
         <v>8902</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>2021</v>
@@ -1468,15 +1297,12 @@
         <v>18250764</v>
       </c>
       <c r="D58">
-        <v>46.73</v>
-      </c>
-      <c r="E58">
         <v>8528</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59">
         <v>2022</v>
@@ -1485,15 +1311,12 @@
         <v>43656515</v>
       </c>
       <c r="D59">
-        <v>37.39</v>
-      </c>
-      <c r="E59">
         <v>16323</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60">
         <v>2023</v>
@@ -1502,15 +1325,12 @@
         <v>22470758</v>
       </c>
       <c r="D60">
-        <v>61.57</v>
-      </c>
-      <c r="E60">
         <v>13835</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B61">
         <v>2024</v>
@@ -1519,15 +1339,12 @@
         <v>21851509</v>
       </c>
       <c r="D61">
-        <v>22.39</v>
-      </c>
-      <c r="E61">
         <v>4892</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62">
         <v>2010</v>
@@ -1536,15 +1353,12 @@
         <v>36593880</v>
       </c>
       <c r="D62">
-        <v>57.83</v>
-      </c>
-      <c r="E62">
         <v>21162</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63">
         <v>2011</v>
@@ -1553,15 +1367,12 @@
         <v>15143995</v>
       </c>
       <c r="D63">
-        <v>11.33</v>
-      </c>
-      <c r="E63">
         <v>1715</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64">
         <v>2012</v>
@@ -1570,15 +1381,12 @@
         <v>44566131</v>
       </c>
       <c r="D64">
-        <v>53.22</v>
-      </c>
-      <c r="E64">
         <v>23718</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65">
         <v>2013</v>
@@ -1587,15 +1395,12 @@
         <v>35255914</v>
       </c>
       <c r="D65">
-        <v>58.55</v>
-      </c>
-      <c r="E65">
         <v>20642</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66">
         <v>2014</v>
@@ -1604,15 +1409,12 @@
         <v>23977595</v>
       </c>
       <c r="D66">
-        <v>24.46</v>
-      </c>
-      <c r="E66">
         <v>5864</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67">
         <v>2015</v>
@@ -1621,15 +1423,12 @@
         <v>2984413</v>
       </c>
       <c r="D67">
-        <v>26.38</v>
-      </c>
-      <c r="E67">
         <v>787</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68">
         <v>2016</v>
@@ -1638,15 +1437,12 @@
         <v>39949976</v>
       </c>
       <c r="D68">
-        <v>11.6</v>
-      </c>
-      <c r="E68">
         <v>4634</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69">
         <v>2017</v>
@@ -1655,15 +1451,12 @@
         <v>2735000</v>
       </c>
       <c r="D69">
-        <v>43.86</v>
-      </c>
-      <c r="E69">
         <v>1199</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70">
         <v>2018</v>
@@ -1672,15 +1465,12 @@
         <v>6322184</v>
       </c>
       <c r="D70">
-        <v>54.08</v>
-      </c>
-      <c r="E70">
         <v>3419</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71">
         <v>2019</v>
@@ -1689,15 +1479,12 @@
         <v>36602853</v>
       </c>
       <c r="D71">
-        <v>23.29</v>
-      </c>
-      <c r="E71">
         <v>8524</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B72">
         <v>2020</v>
@@ -1706,15 +1493,12 @@
         <v>2454109</v>
       </c>
       <c r="D72">
-        <v>35.64</v>
-      </c>
-      <c r="E72">
         <v>874</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73">
         <v>2021</v>
@@ -1723,15 +1507,12 @@
         <v>16766473</v>
       </c>
       <c r="D73">
-        <v>18.329999999999998</v>
-      </c>
-      <c r="E73">
         <v>3073</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74">
         <v>2022</v>
@@ -1740,15 +1521,12 @@
         <v>23734510</v>
       </c>
       <c r="D74">
-        <v>25.26</v>
-      </c>
-      <c r="E74">
         <v>5995</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B75">
         <v>2023</v>
@@ -1757,15 +1535,12 @@
         <v>561087</v>
       </c>
       <c r="D75">
-        <v>15.1</v>
-      </c>
-      <c r="E75">
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76">
         <v>2024</v>
@@ -1774,15 +1549,12 @@
         <v>18773392</v>
       </c>
       <c r="D76">
-        <v>36.130000000000003</v>
-      </c>
-      <c r="E76">
         <v>6782</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77">
         <v>2010</v>
@@ -1791,15 +1563,12 @@
         <v>17316569</v>
       </c>
       <c r="D77">
-        <v>8.89</v>
-      </c>
-      <c r="E77">
         <v>1539</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78">
         <v>2011</v>
@@ -1808,15 +1577,12 @@
         <v>8154909</v>
       </c>
       <c r="D78">
-        <v>62.75</v>
-      </c>
-      <c r="E78">
         <v>5117</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79">
         <v>2012</v>
@@ -1825,15 +1591,12 @@
         <v>39780002</v>
       </c>
       <c r="D79">
-        <v>46.78</v>
-      </c>
-      <c r="E79">
         <v>18609</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B80">
         <v>2013</v>
@@ -1842,15 +1605,12 @@
         <v>15921040</v>
       </c>
       <c r="D80">
-        <v>23.05</v>
-      </c>
-      <c r="E80">
         <v>3669</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B81">
         <v>2014</v>
@@ -1859,15 +1619,12 @@
         <v>5465050</v>
       </c>
       <c r="D81">
-        <v>64.86</v>
-      </c>
-      <c r="E81">
         <v>3544</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B82">
         <v>2015</v>
@@ -1876,15 +1633,12 @@
         <v>12006305</v>
       </c>
       <c r="D82">
-        <v>41.57</v>
-      </c>
-      <c r="E82">
         <v>4991</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B83">
         <v>2016</v>
@@ -1893,15 +1647,12 @@
         <v>8234102</v>
       </c>
       <c r="D83">
-        <v>29.66</v>
-      </c>
-      <c r="E83">
         <v>2442</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B84">
         <v>2017</v>
@@ -1910,15 +1661,12 @@
         <v>9158144</v>
       </c>
       <c r="D84">
-        <v>21.72</v>
-      </c>
-      <c r="E84">
         <v>1989</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B85">
         <v>2018</v>
@@ -1927,15 +1675,12 @@
         <v>38426525</v>
       </c>
       <c r="D85">
-        <v>43.06</v>
-      </c>
-      <c r="E85">
         <v>16546</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B86">
         <v>2019</v>
@@ -1944,15 +1689,12 @@
         <v>22308811</v>
       </c>
       <c r="D86">
-        <v>13.69</v>
-      </c>
-      <c r="E86">
         <v>3054</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B87">
         <v>2020</v>
@@ -1961,15 +1703,12 @@
         <v>26347493</v>
       </c>
       <c r="D87">
-        <v>31.87</v>
-      </c>
-      <c r="E87">
         <v>8396</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B88">
         <v>2021</v>
@@ -1978,15 +1717,12 @@
         <v>1619043</v>
       </c>
       <c r="D88">
-        <v>19.52</v>
-      </c>
-      <c r="E88">
         <v>316</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B89">
         <v>2022</v>
@@ -1995,15 +1731,12 @@
         <v>44649943</v>
       </c>
       <c r="D89">
-        <v>9.85</v>
-      </c>
-      <c r="E89">
         <v>4398</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B90">
         <v>2023</v>
@@ -2012,15 +1745,12 @@
         <v>41157662</v>
       </c>
       <c r="D90">
-        <v>19.260000000000002</v>
-      </c>
-      <c r="E90">
         <v>7926</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91">
         <v>2024</v>
@@ -2029,15 +1759,12 @@
         <v>7159908</v>
       </c>
       <c r="D91">
-        <v>53.19</v>
-      </c>
-      <c r="E91">
         <v>3808</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B92">
         <v>2010</v>
@@ -2046,15 +1773,12 @@
         <v>37134821</v>
       </c>
       <c r="D92">
-        <v>42.94</v>
-      </c>
-      <c r="E92">
         <v>15945</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B93">
         <v>2011</v>
@@ -2063,15 +1787,12 @@
         <v>17387294</v>
       </c>
       <c r="D93">
-        <v>28.93</v>
-      </c>
-      <c r="E93">
         <v>5030</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94">
         <v>2012</v>
@@ -2080,15 +1801,12 @@
         <v>31327104</v>
       </c>
       <c r="D94">
-        <v>10.42</v>
-      </c>
-      <c r="E94">
         <v>3264</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B95">
         <v>2013</v>
@@ -2097,15 +1815,12 @@
         <v>35713498</v>
       </c>
       <c r="D95">
-        <v>14.04</v>
-      </c>
-      <c r="E95">
         <v>5014</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B96">
         <v>2014</v>
@@ -2114,15 +1829,12 @@
         <v>41410172</v>
       </c>
       <c r="D96">
-        <v>16.190000000000001</v>
-      </c>
-      <c r="E96">
         <v>6704</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B97">
         <v>2015</v>
@@ -2131,15 +1843,12 @@
         <v>24935642</v>
       </c>
       <c r="D97">
-        <v>56.5</v>
-      </c>
-      <c r="E97">
         <v>14088</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B98">
         <v>2016</v>
@@ -2148,15 +1857,12 @@
         <v>34965113</v>
       </c>
       <c r="D98">
-        <v>18.21</v>
-      </c>
-      <c r="E98">
         <v>6367</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B99">
         <v>2017</v>
@@ -2165,15 +1871,12 @@
         <v>33767858</v>
       </c>
       <c r="D99">
-        <v>35.729999999999997</v>
-      </c>
-      <c r="E99">
         <v>12065</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B100">
         <v>2018</v>
@@ -2182,15 +1885,12 @@
         <v>10921958</v>
       </c>
       <c r="D100">
-        <v>25.92</v>
-      </c>
-      <c r="E100">
         <v>2830</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B101">
         <v>2019</v>
@@ -2199,15 +1899,12 @@
         <v>15264960</v>
       </c>
       <c r="D101">
-        <v>15.46</v>
-      </c>
-      <c r="E101">
         <v>2359</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B102">
         <v>2020</v>
@@ -2216,15 +1913,12 @@
         <v>9632582</v>
       </c>
       <c r="D102">
-        <v>28.85</v>
-      </c>
-      <c r="E102">
         <v>2778</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B103">
         <v>2021</v>
@@ -2233,15 +1927,12 @@
         <v>16885802</v>
       </c>
       <c r="D103">
-        <v>61.2</v>
-      </c>
-      <c r="E103">
         <v>10334</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B104">
         <v>2022</v>
@@ -2250,15 +1941,12 @@
         <v>18103032</v>
       </c>
       <c r="D104">
-        <v>25.46</v>
-      </c>
-      <c r="E104">
         <v>4609</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105">
         <v>2023</v>
@@ -2267,15 +1955,12 @@
         <v>44299966</v>
       </c>
       <c r="D105">
-        <v>17.54</v>
-      </c>
-      <c r="E105">
         <v>7770</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B106">
         <v>2024</v>
@@ -2284,15 +1969,12 @@
         <v>34609026</v>
       </c>
       <c r="D106">
-        <v>57.64</v>
-      </c>
-      <c r="E106">
         <v>19948</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B107">
         <v>2010</v>
@@ -2301,15 +1983,12 @@
         <v>13728175</v>
       </c>
       <c r="D107">
-        <v>18.71</v>
-      </c>
-      <c r="E107">
         <v>2568</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B108">
         <v>2011</v>
@@ -2318,15 +1997,12 @@
         <v>36259096</v>
       </c>
       <c r="D108">
-        <v>54.03</v>
-      </c>
-      <c r="E108">
         <v>19590</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B109">
         <v>2012</v>
@@ -2335,15 +2011,12 @@
         <v>32614689</v>
       </c>
       <c r="D109">
-        <v>36</v>
-      </c>
-      <c r="E109">
         <v>11741</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B110">
         <v>2013</v>
@@ -2352,15 +2025,12 @@
         <v>28807083</v>
       </c>
       <c r="D110">
-        <v>64.78</v>
-      </c>
-      <c r="E110">
         <v>18661</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B111">
         <v>2014</v>
@@ -2369,15 +2039,12 @@
         <v>33297855</v>
       </c>
       <c r="D111">
-        <v>38.5</v>
-      </c>
-      <c r="E111">
         <v>12819</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B112">
         <v>2015</v>
@@ -2386,15 +2053,12 @@
         <v>23948674</v>
       </c>
       <c r="D112">
-        <v>42.99</v>
-      </c>
-      <c r="E112">
         <v>10295</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113">
         <v>2016</v>
@@ -2403,15 +2067,12 @@
         <v>13003247</v>
       </c>
       <c r="D113">
-        <v>47.02</v>
-      </c>
-      <c r="E113">
         <v>6114</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B114">
         <v>2017</v>
@@ -2420,15 +2081,12 @@
         <v>6541495</v>
       </c>
       <c r="D114">
-        <v>58.83</v>
-      </c>
-      <c r="E114">
         <v>3848</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B115">
         <v>2018</v>
@@ -2437,15 +2095,12 @@
         <v>23601383</v>
       </c>
       <c r="D115">
-        <v>56.06</v>
-      </c>
-      <c r="E115">
         <v>13230</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B116">
         <v>2019</v>
@@ -2454,15 +2109,12 @@
         <v>11502109</v>
       </c>
       <c r="D116">
-        <v>52.12</v>
-      </c>
-      <c r="E116">
         <v>5994</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B117">
         <v>2020</v>
@@ -2471,15 +2123,12 @@
         <v>33663773</v>
       </c>
       <c r="D117">
-        <v>5.55</v>
-      </c>
-      <c r="E117">
         <v>1868</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B118">
         <v>2021</v>
@@ -2488,15 +2137,12 @@
         <v>21604792</v>
       </c>
       <c r="D118">
-        <v>61.41</v>
-      </c>
-      <c r="E118">
         <v>13267</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B119">
         <v>2022</v>
@@ -2505,15 +2151,12 @@
         <v>20076703</v>
       </c>
       <c r="D119">
-        <v>5.3</v>
-      </c>
-      <c r="E119">
         <v>1064</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B120">
         <v>2023</v>
@@ -2522,15 +2165,12 @@
         <v>5820385</v>
       </c>
       <c r="D120">
-        <v>23.32</v>
-      </c>
-      <c r="E120">
         <v>1357</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B121">
         <v>2024</v>
@@ -2539,15 +2179,12 @@
         <v>43803868</v>
       </c>
       <c r="D121">
-        <v>46.51</v>
-      </c>
-      <c r="E121">
         <v>20373</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B122">
         <v>2010</v>
@@ -2556,15 +2193,12 @@
         <v>39387584</v>
       </c>
       <c r="D122">
-        <v>18.46</v>
-      </c>
-      <c r="E122">
         <v>7270</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B123">
         <v>2011</v>
@@ -2573,15 +2207,12 @@
         <v>41382573</v>
       </c>
       <c r="D123">
-        <v>6.08</v>
-      </c>
-      <c r="E123">
         <v>2516</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124">
         <v>2012</v>
@@ -2590,15 +2221,12 @@
         <v>30967575</v>
       </c>
       <c r="D124">
-        <v>24.52</v>
-      </c>
-      <c r="E124">
         <v>7593</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B125">
         <v>2013</v>
@@ -2607,15 +2235,12 @@
         <v>24008102</v>
       </c>
       <c r="D125">
-        <v>43.98</v>
-      </c>
-      <c r="E125">
         <v>10558</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B126">
         <v>2014</v>
@@ -2624,15 +2249,12 @@
         <v>25447744</v>
       </c>
       <c r="D126">
-        <v>48.26</v>
-      </c>
-      <c r="E126">
         <v>12281</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B127">
         <v>2015</v>
@@ -2641,15 +2263,12 @@
         <v>38356186</v>
       </c>
       <c r="D127">
-        <v>37.549999999999997</v>
-      </c>
-      <c r="E127">
         <v>14402</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B128">
         <v>2016</v>
@@ -2658,15 +2277,12 @@
         <v>2483509</v>
       </c>
       <c r="D128">
-        <v>27.06</v>
-      </c>
-      <c r="E128">
         <v>672</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B129">
         <v>2017</v>
@@ -2675,15 +2291,12 @@
         <v>18798917</v>
       </c>
       <c r="D129">
-        <v>19.64</v>
-      </c>
-      <c r="E129">
         <v>3692</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B130">
         <v>2018</v>
@@ -2692,15 +2305,12 @@
         <v>10666834</v>
       </c>
       <c r="D130">
-        <v>63.73</v>
-      </c>
-      <c r="E130">
         <v>6797</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B131">
         <v>2019</v>
@@ -2709,15 +2319,12 @@
         <v>26865210</v>
       </c>
       <c r="D131">
-        <v>58.52</v>
-      </c>
-      <c r="E131">
         <v>15721</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B132">
         <v>2020</v>
@@ -2726,15 +2333,12 @@
         <v>27680308</v>
       </c>
       <c r="D132">
-        <v>31.06</v>
-      </c>
-      <c r="E132">
         <v>8597</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B133">
         <v>2021</v>
@@ -2743,15 +2347,12 @@
         <v>35472607</v>
       </c>
       <c r="D133">
-        <v>35.159999999999997</v>
-      </c>
-      <c r="E133">
         <v>12472</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B134">
         <v>2022</v>
@@ -2760,15 +2361,12 @@
         <v>16400476</v>
       </c>
       <c r="D134">
-        <v>56.85</v>
-      </c>
-      <c r="E134">
         <v>9323</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B135">
         <v>2023</v>
@@ -2777,15 +2375,12 @@
         <v>41320227</v>
       </c>
       <c r="D135">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="E135">
         <v>14441</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B136">
         <v>2024</v>
@@ -2794,15 +2389,12 @@
         <v>21318992</v>
       </c>
       <c r="D136">
-        <v>6.46</v>
-      </c>
-      <c r="E136">
         <v>1377</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137">
         <v>2010</v>
@@ -2811,15 +2403,12 @@
         <v>44203467</v>
       </c>
       <c r="D137">
-        <v>7.62</v>
-      </c>
-      <c r="E137">
         <v>3368</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138">
         <v>2011</v>
@@ -2828,15 +2417,12 @@
         <v>3951356</v>
       </c>
       <c r="D138">
-        <v>61.43</v>
-      </c>
-      <c r="E138">
         <v>2427</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139">
         <v>2012</v>
@@ -2845,15 +2431,12 @@
         <v>36981541</v>
       </c>
       <c r="D139">
-        <v>21.77</v>
-      </c>
-      <c r="E139">
         <v>8050</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140">
         <v>2013</v>
@@ -2862,15 +2445,12 @@
         <v>28174903</v>
       </c>
       <c r="D140">
-        <v>27.21</v>
-      </c>
-      <c r="E140">
         <v>7666</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B141">
         <v>2014</v>
@@ -2879,15 +2459,12 @@
         <v>25797197</v>
       </c>
       <c r="D141">
-        <v>24.85</v>
-      </c>
-      <c r="E141">
         <v>6410</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B142">
         <v>2015</v>
@@ -2896,15 +2473,12 @@
         <v>40269056</v>
       </c>
       <c r="D142">
-        <v>63</v>
-      </c>
-      <c r="E142">
         <v>25369</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B143">
         <v>2016</v>
@@ -2913,15 +2487,12 @@
         <v>38390300</v>
       </c>
       <c r="D143">
-        <v>9.52</v>
-      </c>
-      <c r="E143">
         <v>3654</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144">
         <v>2017</v>
@@ -2930,15 +2501,12 @@
         <v>32225526</v>
       </c>
       <c r="D144">
-        <v>28.11</v>
-      </c>
-      <c r="E144">
         <v>9058</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B145">
         <v>2018</v>
@@ -2947,15 +2515,12 @@
         <v>4386402</v>
       </c>
       <c r="D145">
-        <v>21.11</v>
-      </c>
-      <c r="E145">
         <v>925</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B146">
         <v>2019</v>
@@ -2964,15 +2529,12 @@
         <v>43132984</v>
       </c>
       <c r="D146">
-        <v>15.17</v>
-      </c>
-      <c r="E146">
         <v>6543</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B147">
         <v>2020</v>
@@ -2981,15 +2543,12 @@
         <v>2489173</v>
       </c>
       <c r="D147">
-        <v>28.68</v>
-      </c>
-      <c r="E147">
         <v>713</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B148">
         <v>2021</v>
@@ -2998,15 +2557,12 @@
         <v>32974983</v>
       </c>
       <c r="D148">
-        <v>46.76</v>
-      </c>
-      <c r="E148">
         <v>15419</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B149">
         <v>2022</v>
@@ -3015,15 +2571,12 @@
         <v>25383825</v>
       </c>
       <c r="D149">
-        <v>9.2200000000000006</v>
-      </c>
-      <c r="E149">
         <v>2340</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B150">
         <v>2023</v>
@@ -3032,15 +2585,12 @@
         <v>24890485</v>
       </c>
       <c r="D150">
-        <v>41.9</v>
-      </c>
-      <c r="E150">
         <v>10429</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B151">
         <v>2024</v>
@@ -3049,15 +2599,12 @@
         <v>18382750</v>
       </c>
       <c r="D151">
-        <v>26.52</v>
-      </c>
-      <c r="E151">
         <v>4875</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B152">
         <v>2010</v>
@@ -3066,15 +2613,12 @@
         <v>10692257</v>
       </c>
       <c r="D152">
-        <v>36.1</v>
-      </c>
-      <c r="E152">
         <v>3859</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B153">
         <v>2011</v>
@@ -3083,15 +2627,12 @@
         <v>21630343</v>
       </c>
       <c r="D153">
-        <v>24.35</v>
-      </c>
-      <c r="E153">
         <v>5266</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B154">
         <v>2012</v>
@@ -3100,15 +2641,12 @@
         <v>25350677</v>
       </c>
       <c r="D154">
-        <v>46.82</v>
-      </c>
-      <c r="E154">
         <v>11869</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155">
         <v>2013</v>
@@ -3117,15 +2655,12 @@
         <v>27158609</v>
       </c>
       <c r="D155">
-        <v>26.57</v>
-      </c>
-      <c r="E155">
         <v>7216</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B156">
         <v>2014</v>
@@ -3134,15 +2669,12 @@
         <v>30524204</v>
       </c>
       <c r="D156">
-        <v>57.02</v>
-      </c>
-      <c r="E156">
         <v>17404</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B157">
         <v>2015</v>
@@ -3151,15 +2683,12 @@
         <v>22768806</v>
       </c>
       <c r="D157">
-        <v>9.9</v>
-      </c>
-      <c r="E157">
         <v>2254</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B158">
         <v>2016</v>
@@ -3168,15 +2697,12 @@
         <v>6599628</v>
       </c>
       <c r="D158">
-        <v>35.090000000000003</v>
-      </c>
-      <c r="E158">
         <v>2315</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B159">
         <v>2017</v>
@@ -3185,15 +2711,12 @@
         <v>36753447</v>
       </c>
       <c r="D159">
-        <v>16.66</v>
-      </c>
-      <c r="E159">
         <v>6123</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B160">
         <v>2018</v>
@@ -3202,15 +2725,12 @@
         <v>17222573</v>
       </c>
       <c r="D160">
-        <v>47.12</v>
-      </c>
-      <c r="E160">
         <v>8115</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B161">
         <v>2019</v>
@@ -3219,15 +2739,12 @@
         <v>42892022</v>
       </c>
       <c r="D161">
-        <v>58.4</v>
-      </c>
-      <c r="E161">
         <v>25048</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B162">
         <v>2020</v>
@@ -3236,15 +2753,12 @@
         <v>3677825</v>
       </c>
       <c r="D162">
-        <v>6.66</v>
-      </c>
-      <c r="E162">
         <v>244</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B163">
         <v>2021</v>
@@ -3253,15 +2767,12 @@
         <v>1166326</v>
       </c>
       <c r="D163">
-        <v>10.64</v>
-      </c>
-      <c r="E163">
         <v>124</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B164">
         <v>2022</v>
@@ -3270,15 +2781,12 @@
         <v>618834</v>
       </c>
       <c r="D164">
-        <v>45.32</v>
-      </c>
-      <c r="E164">
         <v>280</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B165">
         <v>2023</v>
@@ -3287,15 +2795,12 @@
         <v>23225756</v>
       </c>
       <c r="D165">
-        <v>32.94</v>
-      </c>
-      <c r="E165">
         <v>7650</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B166">
         <v>2024</v>
@@ -3304,15 +2809,12 @@
         <v>4922201</v>
       </c>
       <c r="D166">
-        <v>55.34</v>
-      </c>
-      <c r="E166">
         <v>2723</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B167">
         <v>2010</v>
@@ -3321,15 +2823,12 @@
         <v>26691539</v>
       </c>
       <c r="D167">
-        <v>6.83</v>
-      </c>
-      <c r="E167">
         <v>1823</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B168">
         <v>2011</v>
@@ -3338,15 +2837,12 @@
         <v>27947054</v>
       </c>
       <c r="D168">
-        <v>7.33</v>
-      </c>
-      <c r="E168">
         <v>2048</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B169">
         <v>2012</v>
@@ -3355,15 +2851,12 @@
         <v>9349851</v>
       </c>
       <c r="D169">
-        <v>26.61</v>
-      </c>
-      <c r="E169">
         <v>2487</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B170">
         <v>2013</v>
@@ -3372,15 +2865,12 @@
         <v>19262804</v>
       </c>
       <c r="D170">
-        <v>24.6</v>
-      </c>
-      <c r="E170">
         <v>4738</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B171">
         <v>2014</v>
@@ -3389,15 +2879,12 @@
         <v>18281862</v>
       </c>
       <c r="D171">
-        <v>21.29</v>
-      </c>
-      <c r="E171">
         <v>3892</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B172">
         <v>2015</v>
@@ -3406,15 +2893,12 @@
         <v>21144716</v>
       </c>
       <c r="D172">
-        <v>10.119999999999999</v>
-      </c>
-      <c r="E172">
         <v>2139</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B173">
         <v>2016</v>
@@ -3423,15 +2907,12 @@
         <v>22421117</v>
       </c>
       <c r="D173">
-        <v>16.66</v>
-      </c>
-      <c r="E173">
         <v>3735</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B174">
         <v>2017</v>
@@ -3440,15 +2921,12 @@
         <v>32030803</v>
       </c>
       <c r="D174">
-        <v>37.44</v>
-      </c>
-      <c r="E174">
         <v>11992</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B175">
         <v>2018</v>
@@ -3457,15 +2935,12 @@
         <v>3879569</v>
       </c>
       <c r="D175">
-        <v>12.96</v>
-      </c>
-      <c r="E175">
         <v>502</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B176">
         <v>2019</v>
@@ -3474,15 +2949,12 @@
         <v>42665906</v>
       </c>
       <c r="D176">
-        <v>35.979999999999997</v>
-      </c>
-      <c r="E176">
         <v>15351</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B177">
         <v>2020</v>
@@ -3491,15 +2963,12 @@
         <v>22864990</v>
       </c>
       <c r="D177">
-        <v>52.71</v>
-      </c>
-      <c r="E177">
         <v>12052</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B178">
         <v>2021</v>
@@ -3508,15 +2977,12 @@
         <v>42022233</v>
       </c>
       <c r="D178">
-        <v>31.01</v>
-      </c>
-      <c r="E178">
         <v>13031</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B179">
         <v>2022</v>
@@ -3525,15 +2991,12 @@
         <v>42271748</v>
       </c>
       <c r="D179">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="E179">
         <v>4104</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B180">
         <v>2023</v>
@@ -3542,15 +3005,12 @@
         <v>12302429</v>
       </c>
       <c r="D180">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="E180">
         <v>1975</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B181">
         <v>2024</v>
@@ -3559,15 +3019,12 @@
         <v>36896424</v>
       </c>
       <c r="D181">
-        <v>55.16</v>
-      </c>
-      <c r="E181">
         <v>20352</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B182">
         <v>2010</v>
@@ -3576,15 +3033,12 @@
         <v>6595929</v>
       </c>
       <c r="D182">
-        <v>46.31</v>
-      </c>
-      <c r="E182">
         <v>3054</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B183">
         <v>2011</v>
@@ -3593,15 +3047,12 @@
         <v>21340174</v>
       </c>
       <c r="D183">
-        <v>59.91</v>
-      </c>
-      <c r="E183">
         <v>12784</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B184">
         <v>2012</v>
@@ -3610,15 +3061,12 @@
         <v>10600349</v>
       </c>
       <c r="D184">
-        <v>20.010000000000002</v>
-      </c>
-      <c r="E184">
         <v>2121</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B185">
         <v>2013</v>
@@ -3627,15 +3075,12 @@
         <v>17453831</v>
       </c>
       <c r="D185">
-        <v>10.63</v>
-      </c>
-      <c r="E185">
         <v>1855</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B186">
         <v>2014</v>
@@ -3644,15 +3089,12 @@
         <v>7974447</v>
       </c>
       <c r="D186">
-        <v>61.08</v>
-      </c>
-      <c r="E186">
         <v>4870</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B187">
         <v>2015</v>
@@ -3661,15 +3103,12 @@
         <v>4199391</v>
       </c>
       <c r="D187">
-        <v>36</v>
-      </c>
-      <c r="E187">
         <v>1511</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B188">
         <v>2016</v>
@@ -3678,15 +3117,12 @@
         <v>10574901</v>
       </c>
       <c r="D188">
-        <v>38.26</v>
-      </c>
-      <c r="E188">
         <v>4045</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B189">
         <v>2017</v>
@@ -3695,15 +3131,12 @@
         <v>4112610</v>
       </c>
       <c r="D189">
-        <v>48.8</v>
-      </c>
-      <c r="E189">
         <v>2006</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B190">
         <v>2018</v>
@@ -3712,15 +3145,12 @@
         <v>10792658</v>
       </c>
       <c r="D190">
-        <v>19.86</v>
-      </c>
-      <c r="E190">
         <v>2143</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B191">
         <v>2019</v>
@@ -3729,15 +3159,12 @@
         <v>29266157</v>
       </c>
       <c r="D191">
-        <v>50.47</v>
-      </c>
-      <c r="E191">
         <v>14770</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B192">
         <v>2020</v>
@@ -3746,15 +3173,12 @@
         <v>2248014</v>
       </c>
       <c r="D192">
-        <v>10.51</v>
-      </c>
-      <c r="E192">
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B193">
         <v>2021</v>
@@ -3763,15 +3187,12 @@
         <v>2788627</v>
       </c>
       <c r="D193">
-        <v>7.44</v>
-      </c>
-      <c r="E193">
         <v>207</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B194">
         <v>2022</v>
@@ -3780,15 +3201,12 @@
         <v>7097519</v>
       </c>
       <c r="D194">
-        <v>15.52</v>
-      </c>
-      <c r="E194">
         <v>1101</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B195">
         <v>2023</v>
@@ -3797,15 +3215,12 @@
         <v>31599311</v>
       </c>
       <c r="D195">
-        <v>10.87</v>
-      </c>
-      <c r="E195">
         <v>3434</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B196">
         <v>2024</v>
@@ -3814,15 +3229,12 @@
         <v>11470723</v>
       </c>
       <c r="D196">
-        <v>53.41</v>
-      </c>
-      <c r="E196">
         <v>6126</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B197">
         <v>2010</v>
@@ -3831,15 +3243,12 @@
         <v>39793284</v>
       </c>
       <c r="D197">
-        <v>15.39</v>
-      </c>
-      <c r="E197">
         <v>6124</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B198">
         <v>2011</v>
@@ -3848,15 +3257,12 @@
         <v>28310313</v>
       </c>
       <c r="D198">
-        <v>28.91</v>
-      </c>
-      <c r="E198">
         <v>8184</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B199">
         <v>2012</v>
@@ -3865,15 +3271,12 @@
         <v>4193305</v>
       </c>
       <c r="D199">
-        <v>61.95</v>
-      </c>
-      <c r="E199">
         <v>2597</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B200">
         <v>2013</v>
@@ -3882,15 +3285,12 @@
         <v>4966271</v>
       </c>
       <c r="D200">
-        <v>61.01</v>
-      </c>
-      <c r="E200">
         <v>3029</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B201">
         <v>2014</v>
@@ -3899,15 +3299,12 @@
         <v>10995300</v>
       </c>
       <c r="D201">
-        <v>56.39</v>
-      </c>
-      <c r="E201">
         <v>6200</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B202">
         <v>2015</v>
@@ -3916,15 +3313,12 @@
         <v>28314927</v>
       </c>
       <c r="D202">
-        <v>46.04</v>
-      </c>
-      <c r="E202">
         <v>13036</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B203">
         <v>2016</v>
@@ -3933,15 +3327,12 @@
         <v>8206358</v>
       </c>
       <c r="D203">
-        <v>9.23</v>
-      </c>
-      <c r="E203">
         <v>757</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B204">
         <v>2017</v>
@@ -3950,15 +3341,12 @@
         <v>34103547</v>
       </c>
       <c r="D204">
-        <v>61.66</v>
-      </c>
-      <c r="E204">
         <v>21028</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B205">
         <v>2018</v>
@@ -3967,15 +3355,12 @@
         <v>12226298</v>
       </c>
       <c r="D205">
-        <v>40.15</v>
-      </c>
-      <c r="E205">
         <v>4908</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B206">
         <v>2019</v>
@@ -3984,15 +3369,12 @@
         <v>23234731</v>
       </c>
       <c r="D206">
-        <v>53.06</v>
-      </c>
-      <c r="E206">
         <v>12328</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B207">
         <v>2020</v>
@@ -4001,15 +3383,12 @@
         <v>11938459</v>
       </c>
       <c r="D207">
-        <v>28.29</v>
-      </c>
-      <c r="E207">
         <v>3377</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B208">
         <v>2021</v>
@@ -4018,15 +3397,12 @@
         <v>35458762</v>
       </c>
       <c r="D208">
-        <v>12.71</v>
-      </c>
-      <c r="E208">
         <v>4506</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B209">
         <v>2022</v>
@@ -4035,15 +3411,12 @@
         <v>34545504</v>
       </c>
       <c r="D209">
-        <v>61.49</v>
-      </c>
-      <c r="E209">
         <v>21242</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B210">
         <v>2023</v>
@@ -4052,15 +3425,12 @@
         <v>15787338</v>
       </c>
       <c r="D210">
-        <v>62.67</v>
-      </c>
-      <c r="E210">
         <v>9893</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B211">
         <v>2024</v>
@@ -4069,15 +3439,12 @@
         <v>29969068</v>
       </c>
       <c r="D211">
-        <v>16.75</v>
-      </c>
-      <c r="E211">
         <v>5019</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B212">
         <v>2010</v>
@@ -4086,15 +3453,12 @@
         <v>10202701</v>
       </c>
       <c r="D212">
-        <v>17.88</v>
-      </c>
-      <c r="E212">
         <v>1824</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B213">
         <v>2011</v>
@@ -4103,15 +3467,12 @@
         <v>3476242</v>
       </c>
       <c r="D213">
-        <v>6.09</v>
-      </c>
-      <c r="E213">
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B214">
         <v>2012</v>
@@ -4120,15 +3481,12 @@
         <v>36703222</v>
       </c>
       <c r="D214">
-        <v>42.1</v>
-      </c>
-      <c r="E214">
         <v>15452</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B215">
         <v>2013</v>
@@ -4137,15 +3495,12 @@
         <v>28312615</v>
       </c>
       <c r="D215">
-        <v>9.27</v>
-      </c>
-      <c r="E215">
         <v>2624</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B216">
         <v>2014</v>
@@ -4154,15 +3509,12 @@
         <v>42327273</v>
       </c>
       <c r="D216">
-        <v>28.12</v>
-      </c>
-      <c r="E216">
         <v>11902</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B217">
         <v>2015</v>
@@ -4171,15 +3523,12 @@
         <v>8954561</v>
       </c>
       <c r="D217">
-        <v>6.4</v>
-      </c>
-      <c r="E217">
         <v>573</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B218">
         <v>2016</v>
@@ -4188,15 +3537,12 @@
         <v>38252003</v>
       </c>
       <c r="D218">
-        <v>20.64</v>
-      </c>
-      <c r="E218">
         <v>7895</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B219">
         <v>2017</v>
@@ -4205,15 +3551,12 @@
         <v>20199313</v>
       </c>
       <c r="D219">
-        <v>46.57</v>
-      </c>
-      <c r="E219">
         <v>9406</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B220">
         <v>2018</v>
@@ -4222,15 +3565,12 @@
         <v>11117244</v>
       </c>
       <c r="D220">
-        <v>42.74</v>
-      </c>
-      <c r="E220">
         <v>4751</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B221">
         <v>2019</v>
@@ -4239,15 +3579,12 @@
         <v>28872244</v>
       </c>
       <c r="D221">
-        <v>7.35</v>
-      </c>
-      <c r="E221">
         <v>2122</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B222">
         <v>2020</v>
@@ -4256,15 +3593,12 @@
         <v>5211075</v>
       </c>
       <c r="D222">
-        <v>63.05</v>
-      </c>
-      <c r="E222">
         <v>3285</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B223">
         <v>2021</v>
@@ -4273,15 +3607,12 @@
         <v>3140328</v>
       </c>
       <c r="D223">
-        <v>15.65</v>
-      </c>
-      <c r="E223">
         <v>491</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B224">
         <v>2022</v>
@@ -4290,15 +3621,12 @@
         <v>26828752</v>
       </c>
       <c r="D224">
-        <v>39.11</v>
-      </c>
-      <c r="E224">
         <v>10492</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B225">
         <v>2023</v>
@@ -4307,15 +3635,12 @@
         <v>12052291</v>
       </c>
       <c r="D225">
-        <v>48.9</v>
-      </c>
-      <c r="E225">
         <v>5893</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B226">
         <v>2024</v>
@@ -4324,15 +3649,12 @@
         <v>10889599</v>
       </c>
       <c r="D226">
-        <v>27.32</v>
-      </c>
-      <c r="E226">
         <v>2975</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B227">
         <v>2010</v>
@@ -4341,15 +3663,12 @@
         <v>38649309</v>
       </c>
       <c r="D227">
-        <v>25.45</v>
-      </c>
-      <c r="E227">
         <v>9836</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B228">
         <v>2011</v>
@@ -4358,15 +3677,12 @@
         <v>18632747</v>
       </c>
       <c r="D228">
-        <v>38.71</v>
-      </c>
-      <c r="E228">
         <v>7212</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B229">
         <v>2012</v>
@@ -4375,15 +3691,12 @@
         <v>4241196</v>
       </c>
       <c r="D229">
-        <v>30.74</v>
-      </c>
-      <c r="E229">
         <v>1303</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B230">
         <v>2013</v>
@@ -4392,15 +3705,12 @@
         <v>17083522</v>
       </c>
       <c r="D230">
-        <v>49.39</v>
-      </c>
-      <c r="E230">
         <v>8437</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B231">
         <v>2014</v>
@@ -4409,15 +3719,12 @@
         <v>13717648</v>
       </c>
       <c r="D231">
-        <v>11.19</v>
-      </c>
-      <c r="E231">
         <v>1535</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B232">
         <v>2015</v>
@@ -4426,15 +3733,12 @@
         <v>32925301</v>
       </c>
       <c r="D232">
-        <v>35.32</v>
-      </c>
-      <c r="E232">
         <v>11629</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B233">
         <v>2016</v>
@@ -4443,15 +3747,12 @@
         <v>27278642</v>
       </c>
       <c r="D233">
-        <v>22.86</v>
-      </c>
-      <c r="E233">
         <v>6235</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B234">
         <v>2017</v>
@@ -4460,15 +3761,12 @@
         <v>23763676</v>
       </c>
       <c r="D234">
-        <v>28.35</v>
-      </c>
-      <c r="E234">
         <v>6737</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B235">
         <v>2018</v>
@@ -4477,15 +3775,12 @@
         <v>29764326</v>
       </c>
       <c r="D235">
-        <v>59.32</v>
-      </c>
-      <c r="E235">
         <v>17656</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B236">
         <v>2019</v>
@@ -4494,15 +3789,12 @@
         <v>21523454</v>
       </c>
       <c r="D236">
-        <v>62.41</v>
-      </c>
-      <c r="E236">
         <v>13432</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B237">
         <v>2020</v>
@@ -4511,15 +3803,12 @@
         <v>37654297</v>
       </c>
       <c r="D237">
-        <v>62.04</v>
-      </c>
-      <c r="E237">
         <v>23360</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B238">
         <v>2021</v>
@@ -4528,15 +3817,12 @@
         <v>37827243</v>
       </c>
       <c r="D238">
-        <v>42.91</v>
-      </c>
-      <c r="E238">
         <v>16231</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B239">
         <v>2022</v>
@@ -4545,15 +3831,12 @@
         <v>3263642</v>
       </c>
       <c r="D239">
-        <v>24.72</v>
-      </c>
-      <c r="E239">
         <v>806</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B240">
         <v>2023</v>
@@ -4562,15 +3845,12 @@
         <v>37842772</v>
       </c>
       <c r="D240">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="E240">
         <v>6720</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B241">
         <v>2024</v>
@@ -4579,15 +3859,12 @@
         <v>36440920</v>
       </c>
       <c r="D241">
-        <v>52.49</v>
-      </c>
-      <c r="E241">
         <v>19127</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B242">
         <v>2010</v>
@@ -4596,15 +3873,12 @@
         <v>39387092</v>
       </c>
       <c r="D242">
-        <v>11.81</v>
-      </c>
-      <c r="E242">
         <v>4651</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B243">
         <v>2011</v>
@@ -4613,15 +3887,12 @@
         <v>11898366</v>
       </c>
       <c r="D243">
-        <v>34.67</v>
-      </c>
-      <c r="E243">
         <v>4125</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B244">
         <v>2012</v>
@@ -4630,15 +3901,12 @@
         <v>11926978</v>
       </c>
       <c r="D244">
-        <v>8.35</v>
-      </c>
-      <c r="E244">
         <v>995</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B245">
         <v>2013</v>
@@ -4647,15 +3915,12 @@
         <v>31273482</v>
       </c>
       <c r="D245">
-        <v>58.26</v>
-      </c>
-      <c r="E245">
         <v>18219</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B246">
         <v>2014</v>
@@ -4664,15 +3929,12 @@
         <v>10664811</v>
       </c>
       <c r="D246">
-        <v>47.35</v>
-      </c>
-      <c r="E246">
         <v>5049</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B247">
         <v>2015</v>
@@ -4681,15 +3943,12 @@
         <v>38462681</v>
       </c>
       <c r="D247">
-        <v>46.28</v>
-      </c>
-      <c r="E247">
         <v>17800</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B248">
         <v>2016</v>
@@ -4698,15 +3957,12 @@
         <v>32165404</v>
       </c>
       <c r="D248">
-        <v>42.09</v>
-      </c>
-      <c r="E248">
         <v>13538</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B249">
         <v>2017</v>
@@ -4715,15 +3971,12 @@
         <v>18609613</v>
       </c>
       <c r="D249">
-        <v>55.31</v>
-      </c>
-      <c r="E249">
         <v>10292</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B250">
         <v>2018</v>
@@ -4732,15 +3985,12 @@
         <v>44579273</v>
       </c>
       <c r="D250">
-        <v>47.06</v>
-      </c>
-      <c r="E250">
         <v>20979</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B251">
         <v>2019</v>
@@ -4749,15 +3999,12 @@
         <v>5962810</v>
       </c>
       <c r="D251">
-        <v>28.8</v>
-      </c>
-      <c r="E251">
         <v>1717</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B252">
         <v>2020</v>
@@ -4766,15 +4013,12 @@
         <v>14346020</v>
       </c>
       <c r="D252">
-        <v>47.37</v>
-      </c>
-      <c r="E252">
         <v>6795</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B253">
         <v>2021</v>
@@ -4783,15 +4027,12 @@
         <v>10226290</v>
       </c>
       <c r="D253">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="E253">
         <v>3661</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B254">
         <v>2022</v>
@@ -4800,15 +4041,12 @@
         <v>16664204</v>
       </c>
       <c r="D254">
-        <v>39.880000000000003</v>
-      </c>
-      <c r="E254">
         <v>6645</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B255">
         <v>2023</v>
@@ -4817,15 +4055,12 @@
         <v>1786643</v>
       </c>
       <c r="D255">
-        <v>27.24</v>
-      </c>
-      <c r="E255">
         <v>486</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B256">
         <v>2024</v>
@@ -4834,15 +4069,12 @@
         <v>6700646</v>
       </c>
       <c r="D256">
-        <v>19.2</v>
-      </c>
-      <c r="E256">
         <v>1286</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B257">
         <v>2010</v>
@@ -4851,15 +4083,12 @@
         <v>15009187</v>
       </c>
       <c r="D257">
-        <v>64.16</v>
-      </c>
-      <c r="E257">
         <v>9629</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B258">
         <v>2011</v>
@@ -4868,15 +4097,12 @@
         <v>22216219</v>
       </c>
       <c r="D258">
-        <v>26.01</v>
-      </c>
-      <c r="E258">
         <v>5778</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B259">
         <v>2012</v>
@@ -4885,15 +4111,12 @@
         <v>13331595</v>
       </c>
       <c r="D259">
-        <v>10.01</v>
-      </c>
-      <c r="E259">
         <v>1334</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B260">
         <v>2013</v>
@@ -4902,15 +4125,12 @@
         <v>10580346</v>
       </c>
       <c r="D260">
-        <v>38.5</v>
-      </c>
-      <c r="E260">
         <v>4073</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B261">
         <v>2014</v>
@@ -4919,15 +4139,12 @@
         <v>9637682</v>
       </c>
       <c r="D261">
-        <v>19.920000000000002</v>
-      </c>
-      <c r="E261">
         <v>1919</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B262">
         <v>2015</v>
@@ -4936,15 +4153,12 @@
         <v>35933922</v>
       </c>
       <c r="D262">
-        <v>11.67</v>
-      </c>
-      <c r="E262">
         <v>4193</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B263">
         <v>2016</v>
@@ -4953,15 +4167,12 @@
         <v>39038877</v>
       </c>
       <c r="D263">
-        <v>20.22</v>
-      </c>
-      <c r="E263">
         <v>7893</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B264">
         <v>2017</v>
@@ -4970,15 +4181,12 @@
         <v>41057019</v>
       </c>
       <c r="D264">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="E264">
         <v>3440</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B265">
         <v>2018</v>
@@ -4987,15 +4195,12 @@
         <v>44696734</v>
       </c>
       <c r="D265">
-        <v>51.03</v>
-      </c>
-      <c r="E265">
         <v>22808</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B266">
         <v>2019</v>
@@ -5004,15 +4209,12 @@
         <v>39860898</v>
       </c>
       <c r="D266">
-        <v>43.95</v>
-      </c>
-      <c r="E266">
         <v>17518</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B267">
         <v>2020</v>
@@ -5021,15 +4223,12 @@
         <v>39358941</v>
       </c>
       <c r="D267">
-        <v>40</v>
-      </c>
-      <c r="E267">
         <v>15743</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B268">
         <v>2021</v>
@@ -5038,15 +4237,12 @@
         <v>39003931</v>
       </c>
       <c r="D268">
-        <v>29.01</v>
-      </c>
-      <c r="E268">
         <v>11315</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B269">
         <v>2022</v>
@@ -5055,15 +4251,12 @@
         <v>40117335</v>
       </c>
       <c r="D269">
-        <v>22.14</v>
-      </c>
-      <c r="E269">
         <v>8881</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B270">
         <v>2023</v>
@@ -5072,15 +4265,12 @@
         <v>43868581</v>
       </c>
       <c r="D270">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="E270">
         <v>16099</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B271">
         <v>2024</v>
@@ -5089,15 +4279,12 @@
         <v>39801804</v>
       </c>
       <c r="D271">
-        <v>53.13</v>
-      </c>
-      <c r="E271">
         <v>21146</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B272">
         <v>2010</v>
@@ -5106,15 +4293,12 @@
         <v>44250190</v>
       </c>
       <c r="D272">
-        <v>63.19</v>
-      </c>
-      <c r="E272">
         <v>27961</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B273">
         <v>2011</v>
@@ -5123,15 +4307,12 @@
         <v>12389876</v>
       </c>
       <c r="D273">
-        <v>58.47</v>
-      </c>
-      <c r="E273">
         <v>7244</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B274">
         <v>2012</v>
@@ -5140,15 +4321,12 @@
         <v>13342659</v>
       </c>
       <c r="D274">
-        <v>64.58</v>
-      </c>
-      <c r="E274">
         <v>8616</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B275">
         <v>2013</v>
@@ -5157,15 +4335,12 @@
         <v>2873139</v>
       </c>
       <c r="D275">
-        <v>38.229999999999997</v>
-      </c>
-      <c r="E275">
         <v>1098</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B276">
         <v>2014</v>
@@ -5174,15 +4349,12 @@
         <v>43301198</v>
       </c>
       <c r="D276">
-        <v>9.5299999999999994</v>
-      </c>
-      <c r="E276">
         <v>4126</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B277">
         <v>2015</v>
@@ -5191,15 +4363,12 @@
         <v>35927853</v>
       </c>
       <c r="D277">
-        <v>42.76</v>
-      </c>
-      <c r="E277">
         <v>15362</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B278">
         <v>2016</v>
@@ -5208,15 +4377,12 @@
         <v>11486868</v>
       </c>
       <c r="D278">
-        <v>22.67</v>
-      </c>
-      <c r="E278">
         <v>2604</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B279">
         <v>2017</v>
@@ -5225,15 +4391,12 @@
         <v>40021538</v>
       </c>
       <c r="D279">
-        <v>46.82</v>
-      </c>
-      <c r="E279">
         <v>18738</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B280">
         <v>2018</v>
@@ -5242,15 +4405,12 @@
         <v>39173354</v>
       </c>
       <c r="D280">
-        <v>59.07</v>
-      </c>
-      <c r="E280">
         <v>23139</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B281">
         <v>2019</v>
@@ -5259,15 +4419,12 @@
         <v>17236613</v>
       </c>
       <c r="D281">
-        <v>21.86</v>
-      </c>
-      <c r="E281">
         <v>3767</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B282">
         <v>2020</v>
@@ -5276,15 +4433,12 @@
         <v>32862868</v>
       </c>
       <c r="D282">
-        <v>32.340000000000003</v>
-      </c>
-      <c r="E282">
         <v>10627</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B283">
         <v>2021</v>
@@ -5293,15 +4447,12 @@
         <v>3167867</v>
       </c>
       <c r="D283">
-        <v>21.64</v>
-      </c>
-      <c r="E283">
         <v>685</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B284">
         <v>2022</v>
@@ -5310,15 +4461,12 @@
         <v>41741273</v>
       </c>
       <c r="D284">
-        <v>43.81</v>
-      </c>
-      <c r="E284">
         <v>18286</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B285">
         <v>2023</v>
@@ -5327,15 +4475,12 @@
         <v>1844027</v>
       </c>
       <c r="D285">
-        <v>18.760000000000002</v>
-      </c>
-      <c r="E285">
         <v>345</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B286">
         <v>2024</v>
@@ -5344,15 +4489,12 @@
         <v>24744264</v>
       </c>
       <c r="D286">
-        <v>9.66</v>
-      </c>
-      <c r="E286">
         <v>2390</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B287">
         <v>2010</v>
@@ -5361,15 +4503,12 @@
         <v>997562</v>
       </c>
       <c r="D287">
-        <v>20.6</v>
-      </c>
-      <c r="E287">
         <v>205</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B288">
         <v>2011</v>
@@ -5378,15 +4517,12 @@
         <v>21314992</v>
       </c>
       <c r="D288">
-        <v>46.89</v>
-      </c>
-      <c r="E288">
         <v>9994</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B289">
         <v>2012</v>
@@ -5395,15 +4531,12 @@
         <v>21788948</v>
       </c>
       <c r="D289">
-        <v>21.79</v>
-      </c>
-      <c r="E289">
         <v>4747</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B290">
         <v>2013</v>
@@ -5412,15 +4545,12 @@
         <v>23403535</v>
       </c>
       <c r="D290">
-        <v>53.83</v>
-      </c>
-      <c r="E290">
         <v>12598</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B291">
         <v>2014</v>
@@ -5429,15 +4559,12 @@
         <v>20588365</v>
       </c>
       <c r="D291">
-        <v>14.76</v>
-      </c>
-      <c r="E291">
         <v>3038</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B292">
         <v>2015</v>
@@ -5446,15 +4573,12 @@
         <v>13521573</v>
       </c>
       <c r="D292">
-        <v>9.57</v>
-      </c>
-      <c r="E292">
         <v>1294</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B293">
         <v>2016</v>
@@ -5463,15 +4587,12 @@
         <v>30433823</v>
       </c>
       <c r="D293">
-        <v>61.99</v>
-      </c>
-      <c r="E293">
         <v>18865</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B294">
         <v>2017</v>
@@ -5480,15 +4601,12 @@
         <v>20357417</v>
       </c>
       <c r="D294">
-        <v>39.869999999999997</v>
-      </c>
-      <c r="E294">
         <v>8116</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B295">
         <v>2018</v>
@@ -5497,15 +4615,12 @@
         <v>29228561</v>
       </c>
       <c r="D295">
-        <v>60.96</v>
-      </c>
-      <c r="E295">
         <v>17817</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B296">
         <v>2019</v>
@@ -5514,15 +4629,12 @@
         <v>37369124</v>
       </c>
       <c r="D296">
-        <v>38.1</v>
-      </c>
-      <c r="E296">
         <v>14237</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B297">
         <v>2020</v>
@@ -5531,15 +4643,12 @@
         <v>6785088</v>
       </c>
       <c r="D297">
-        <v>6.58</v>
-      </c>
-      <c r="E297">
         <v>446</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B298">
         <v>2021</v>
@@ -5548,15 +4657,12 @@
         <v>12960255</v>
       </c>
       <c r="D298">
-        <v>51.66</v>
-      </c>
-      <c r="E298">
         <v>6695</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B299">
         <v>2022</v>
@@ -5565,15 +4671,12 @@
         <v>7968810</v>
       </c>
       <c r="D299">
-        <v>64.12</v>
-      </c>
-      <c r="E299">
         <v>5109</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B300">
         <v>2023</v>
@@ -5582,15 +4685,12 @@
         <v>25801054</v>
       </c>
       <c r="D300">
-        <v>40.65</v>
-      </c>
-      <c r="E300">
         <v>10488</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B301">
         <v>2024</v>
@@ -5599,15 +4699,12 @@
         <v>4963418</v>
       </c>
       <c r="D301">
-        <v>28.58</v>
-      </c>
-      <c r="E301">
         <v>1418</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B302">
         <v>2010</v>
@@ -5616,15 +4713,12 @@
         <v>44324588</v>
       </c>
       <c r="D302">
-        <v>55.53</v>
-      </c>
-      <c r="E302">
         <v>24613</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B303">
         <v>2011</v>
@@ -5633,15 +4727,12 @@
         <v>24430984</v>
       </c>
       <c r="D303">
-        <v>8.81</v>
-      </c>
-      <c r="E303">
         <v>2152</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B304">
         <v>2012</v>
@@ -5650,15 +4741,12 @@
         <v>33923744</v>
       </c>
       <c r="D304">
-        <v>29.89</v>
-      </c>
-      <c r="E304">
         <v>10139</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B305">
         <v>2013</v>
@@ -5667,15 +4755,12 @@
         <v>23466789</v>
       </c>
       <c r="D305">
-        <v>5.82</v>
-      </c>
-      <c r="E305">
         <v>1365</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B306">
         <v>2014</v>
@@ -5684,15 +4769,12 @@
         <v>13798372</v>
       </c>
       <c r="D306">
-        <v>46.5</v>
-      </c>
-      <c r="E306">
         <v>6416</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B307">
         <v>2015</v>
@@ -5701,15 +4783,12 @@
         <v>30202914</v>
       </c>
       <c r="D307">
-        <v>64.98</v>
-      </c>
-      <c r="E307">
         <v>19625</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B308">
         <v>2016</v>
@@ -5718,15 +4797,12 @@
         <v>14941444</v>
       </c>
       <c r="D308">
-        <v>38.33</v>
-      </c>
-      <c r="E308">
         <v>5727</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B309">
         <v>2017</v>
@@ -5735,15 +4811,12 @@
         <v>30913513</v>
       </c>
       <c r="D309">
-        <v>48.57</v>
-      </c>
-      <c r="E309">
         <v>15014</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B310">
         <v>2018</v>
@@ -5752,15 +4825,12 @@
         <v>29318516</v>
       </c>
       <c r="D310">
-        <v>55.98</v>
-      </c>
-      <c r="E310">
         <v>16412</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B311">
         <v>2019</v>
@@ -5769,15 +4839,12 @@
         <v>18364557</v>
       </c>
       <c r="D311">
-        <v>32.03</v>
-      </c>
-      <c r="E311">
         <v>5882</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B312">
         <v>2020</v>
@@ -5786,15 +4853,12 @@
         <v>39613388</v>
       </c>
       <c r="D312">
-        <v>20.09</v>
-      </c>
-      <c r="E312">
         <v>7958</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B313">
         <v>2021</v>
@@ -5803,15 +4867,12 @@
         <v>42989277</v>
       </c>
       <c r="D313">
-        <v>41.37</v>
-      </c>
-      <c r="E313">
         <v>17784</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B314">
         <v>2022</v>
@@ -5820,15 +4881,12 @@
         <v>30561031</v>
       </c>
       <c r="D314">
-        <v>57.69</v>
-      </c>
-      <c r="E314">
         <v>17630</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B315">
         <v>2023</v>
@@ -5837,15 +4895,12 @@
         <v>13588862</v>
       </c>
       <c r="D315">
-        <v>42.09</v>
-      </c>
-      <c r="E315">
         <v>5719</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B316">
         <v>2024</v>
@@ -5854,15 +4909,12 @@
         <v>20612033</v>
       </c>
       <c r="D316">
-        <v>11.81</v>
-      </c>
-      <c r="E316">
         <v>2434</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B317">
         <v>2010</v>
@@ -5871,15 +4923,12 @@
         <v>14443554</v>
       </c>
       <c r="D317">
-        <v>33.57</v>
-      </c>
-      <c r="E317">
         <v>4848</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B318">
         <v>2011</v>
@@ -5888,15 +4937,12 @@
         <v>36713003</v>
       </c>
       <c r="D318">
-        <v>36.21</v>
-      </c>
-      <c r="E318">
         <v>13293</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B319">
         <v>2012</v>
@@ -5905,15 +4951,12 @@
         <v>44666109</v>
       </c>
       <c r="D319">
-        <v>53.98</v>
-      </c>
-      <c r="E319">
         <v>24110</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B320">
         <v>2013</v>
@@ -5922,15 +4965,12 @@
         <v>39220111</v>
       </c>
       <c r="D320">
-        <v>57.6</v>
-      </c>
-      <c r="E320">
         <v>22590</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B321">
         <v>2014</v>
@@ -5939,15 +4979,12 @@
         <v>22564334</v>
       </c>
       <c r="D321">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="E321">
         <v>7626</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B322">
         <v>2015</v>
@@ -5956,15 +4993,12 @@
         <v>4600673</v>
       </c>
       <c r="D322">
-        <v>52.08</v>
-      </c>
-      <c r="E322">
         <v>2396</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B323">
         <v>2016</v>
@@ -5973,15 +5007,12 @@
         <v>34381791</v>
       </c>
       <c r="D323">
-        <v>53.3</v>
-      </c>
-      <c r="E323">
         <v>18325</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B324">
         <v>2017</v>
@@ -5990,15 +5021,12 @@
         <v>29867077</v>
       </c>
       <c r="D324">
-        <v>5.87</v>
-      </c>
-      <c r="E324">
         <v>1753</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B325">
         <v>2018</v>
@@ -6007,15 +5035,12 @@
         <v>7453757</v>
       </c>
       <c r="D325">
-        <v>41.49</v>
-      </c>
-      <c r="E325">
         <v>3092</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B326">
         <v>2019</v>
@@ -6024,15 +5049,12 @@
         <v>33343745</v>
       </c>
       <c r="D326">
-        <v>38.29</v>
-      </c>
-      <c r="E326">
         <v>12767</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B327">
         <v>2020</v>
@@ -6041,15 +5063,12 @@
         <v>10820855</v>
       </c>
       <c r="D327">
-        <v>25.9</v>
-      </c>
-      <c r="E327">
         <v>2802</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B328">
         <v>2021</v>
@@ -6058,15 +5077,12 @@
         <v>5157693</v>
       </c>
       <c r="D328">
-        <v>59.63</v>
-      </c>
-      <c r="E328">
         <v>3075</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B329">
         <v>2022</v>
@@ -6075,15 +5091,12 @@
         <v>13336402</v>
       </c>
       <c r="D329">
-        <v>42.33</v>
-      </c>
-      <c r="E329">
         <v>5645</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B330">
         <v>2023</v>
@@ -6092,15 +5105,12 @@
         <v>28196003</v>
       </c>
       <c r="D330">
-        <v>46.86</v>
-      </c>
-      <c r="E330">
         <v>13212</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B331">
         <v>2024</v>
@@ -6109,15 +5119,12 @@
         <v>33748585</v>
       </c>
       <c r="D331">
-        <v>32.56</v>
-      </c>
-      <c r="E331">
         <v>10988</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B332">
         <v>2010</v>
@@ -6126,15 +5133,12 @@
         <v>16545907</v>
       </c>
       <c r="D332">
-        <v>51.14</v>
-      </c>
-      <c r="E332">
         <v>8461</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B333">
         <v>2011</v>
@@ -6143,15 +5147,12 @@
         <v>35903828</v>
       </c>
       <c r="D333">
-        <v>32.549999999999997</v>
-      </c>
-      <c r="E333">
         <v>11686</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6160,15 +5161,12 @@
         <v>26294685</v>
       </c>
       <c r="D334">
-        <v>25.84</v>
-      </c>
-      <c r="E334">
         <v>6794</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B335">
         <v>2013</v>
@@ -6177,15 +5175,12 @@
         <v>25284623</v>
       </c>
       <c r="D335">
-        <v>43</v>
-      </c>
-      <c r="E335">
         <v>10872</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B336">
         <v>2014</v>
@@ -6194,15 +5189,12 @@
         <v>26327438</v>
       </c>
       <c r="D336">
-        <v>25.49</v>
-      </c>
-      <c r="E336">
         <v>6710</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B337">
         <v>2015</v>
@@ -6211,15 +5203,12 @@
         <v>13581782</v>
       </c>
       <c r="D337">
-        <v>12.73</v>
-      </c>
-      <c r="E337">
         <v>1728</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B338">
         <v>2016</v>
@@ -6228,15 +5217,12 @@
         <v>42055914</v>
       </c>
       <c r="D338">
-        <v>40.090000000000003</v>
-      </c>
-      <c r="E338">
         <v>16860</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B339">
         <v>2017</v>
@@ -6245,15 +5231,12 @@
         <v>1572647</v>
       </c>
       <c r="D339">
-        <v>13.33</v>
-      </c>
-      <c r="E339">
         <v>209</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B340">
         <v>2018</v>
@@ -6262,15 +5245,12 @@
         <v>39160995</v>
       </c>
       <c r="D340">
-        <v>15.8</v>
-      </c>
-      <c r="E340">
         <v>6187</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B341">
         <v>2019</v>
@@ -6279,15 +5259,12 @@
         <v>26971618</v>
       </c>
       <c r="D341">
-        <v>25.74</v>
-      </c>
-      <c r="E341">
         <v>6942</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B342">
         <v>2020</v>
@@ -6296,15 +5273,12 @@
         <v>19227583</v>
       </c>
       <c r="D342">
-        <v>57.46</v>
-      </c>
-      <c r="E342">
         <v>11048</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B343">
         <v>2021</v>
@@ -6313,15 +5287,12 @@
         <v>21068697</v>
       </c>
       <c r="D343">
-        <v>15.34</v>
-      </c>
-      <c r="E343">
         <v>3231</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B344">
         <v>2022</v>
@@ -6330,15 +5301,12 @@
         <v>40402996</v>
       </c>
       <c r="D344">
-        <v>18.43</v>
-      </c>
-      <c r="E344">
         <v>7446</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B345">
         <v>2023</v>
@@ -6347,15 +5315,12 @@
         <v>17118153</v>
       </c>
       <c r="D345">
-        <v>15.14</v>
-      </c>
-      <c r="E345">
         <v>2591</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B346">
         <v>2024</v>
@@ -6364,15 +5329,12 @@
         <v>8404069</v>
       </c>
       <c r="D346">
-        <v>15.62</v>
-      </c>
-      <c r="E346">
         <v>1312</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B347">
         <v>2010</v>
@@ -6381,15 +5343,12 @@
         <v>33372680</v>
       </c>
       <c r="D347">
-        <v>12.24</v>
-      </c>
-      <c r="E347">
         <v>4084</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B348">
         <v>2011</v>
@@ -6398,15 +5357,12 @@
         <v>15928653</v>
       </c>
       <c r="D348">
-        <v>26.36</v>
-      </c>
-      <c r="E348">
         <v>4198</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B349">
         <v>2012</v>
@@ -6415,15 +5371,12 @@
         <v>15177069</v>
       </c>
       <c r="D349">
-        <v>26.86</v>
-      </c>
-      <c r="E349">
         <v>4076</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B350">
         <v>2013</v>
@@ -6432,15 +5385,12 @@
         <v>39510202</v>
       </c>
       <c r="D350">
-        <v>24.81</v>
-      </c>
-      <c r="E350">
         <v>9802</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B351">
         <v>2014</v>
@@ -6449,15 +5399,12 @@
         <v>11389464</v>
       </c>
       <c r="D351">
-        <v>7.36</v>
-      </c>
-      <c r="E351">
         <v>838</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B352">
         <v>2015</v>
@@ -6466,15 +5413,12 @@
         <v>1722869</v>
       </c>
       <c r="D352">
-        <v>33.869999999999997</v>
-      </c>
-      <c r="E352">
         <v>583</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B353">
         <v>2016</v>
@@ -6483,15 +5427,12 @@
         <v>3625354</v>
       </c>
       <c r="D353">
-        <v>9.91</v>
-      </c>
-      <c r="E353">
         <v>359</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B354">
         <v>2017</v>
@@ -6500,15 +5441,12 @@
         <v>11645552</v>
       </c>
       <c r="D354">
-        <v>60.25</v>
-      </c>
-      <c r="E354">
         <v>7016</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B355">
         <v>2018</v>
@@ -6517,15 +5455,12 @@
         <v>40556064</v>
       </c>
       <c r="D355">
-        <v>21.61</v>
-      </c>
-      <c r="E355">
         <v>8764</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B356">
         <v>2019</v>
@@ -6534,15 +5469,12 @@
         <v>15652994</v>
       </c>
       <c r="D356">
-        <v>10.07</v>
-      </c>
-      <c r="E356">
         <v>1576</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B357">
         <v>2020</v>
@@ -6551,15 +5483,12 @@
         <v>27233262</v>
       </c>
       <c r="D357">
-        <v>16.07</v>
-      </c>
-      <c r="E357">
         <v>4376</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B358">
         <v>2021</v>
@@ -6568,15 +5497,12 @@
         <v>9806167</v>
       </c>
       <c r="D358">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="E358">
         <v>3647</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B359">
         <v>2022</v>
@@ -6585,15 +5511,12 @@
         <v>38638329</v>
       </c>
       <c r="D359">
-        <v>34.07</v>
-      </c>
-      <c r="E359">
         <v>13164</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B360">
         <v>2023</v>
@@ -6602,15 +5525,12 @@
         <v>567661</v>
       </c>
       <c r="D360">
-        <v>50.6</v>
-      </c>
-      <c r="E360">
         <v>287</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B361">
         <v>2024</v>
@@ -6619,15 +5539,12 @@
         <v>23835437</v>
       </c>
       <c r="D361">
-        <v>32.75</v>
-      </c>
-      <c r="E361">
         <v>7806</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B362">
         <v>2010</v>
@@ -6636,15 +5553,12 @@
         <v>35361938</v>
       </c>
       <c r="D362">
-        <v>13.86</v>
-      </c>
-      <c r="E362">
         <v>4901</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B363">
         <v>2011</v>
@@ -6653,15 +5567,12 @@
         <v>20178830</v>
       </c>
       <c r="D363">
-        <v>47.8</v>
-      </c>
-      <c r="E363">
         <v>9645</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B364">
         <v>2012</v>
@@ -6670,15 +5581,12 @@
         <v>4208654</v>
       </c>
       <c r="D364">
-        <v>55.67</v>
-      </c>
-      <c r="E364">
         <v>2342</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B365">
         <v>2013</v>
@@ -6687,15 +5595,12 @@
         <v>34172465</v>
       </c>
       <c r="D365">
-        <v>6.83</v>
-      </c>
-      <c r="E365">
         <v>2333</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B366">
         <v>2014</v>
@@ -6704,15 +5609,12 @@
         <v>6372354</v>
       </c>
       <c r="D366">
-        <v>31.84</v>
-      </c>
-      <c r="E366">
         <v>2028</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B367">
         <v>2015</v>
@@ -6721,15 +5623,12 @@
         <v>16040184</v>
       </c>
       <c r="D367">
-        <v>28.83</v>
-      </c>
-      <c r="E367">
         <v>4624</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B368">
         <v>2016</v>
@@ -6738,15 +5637,12 @@
         <v>19596265</v>
       </c>
       <c r="D368">
-        <v>49.24</v>
-      </c>
-      <c r="E368">
         <v>9649</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B369">
         <v>2017</v>
@@ -6755,15 +5651,12 @@
         <v>36247046</v>
       </c>
       <c r="D369">
-        <v>38.840000000000003</v>
-      </c>
-      <c r="E369">
         <v>14078</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B370">
         <v>2018</v>
@@ -6772,15 +5665,12 @@
         <v>18047389</v>
       </c>
       <c r="D370">
-        <v>10.35</v>
-      </c>
-      <c r="E370">
         <v>1867</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B371">
         <v>2019</v>
@@ -6789,15 +5679,12 @@
         <v>22919480</v>
       </c>
       <c r="D371">
-        <v>12.19</v>
-      </c>
-      <c r="E371">
         <v>2793</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B372">
         <v>2020</v>
@@ -6806,15 +5693,12 @@
         <v>34521442</v>
       </c>
       <c r="D372">
-        <v>45.75</v>
-      </c>
-      <c r="E372">
         <v>15793</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B373">
         <v>2021</v>
@@ -6823,15 +5707,12 @@
         <v>38275470</v>
       </c>
       <c r="D373">
-        <v>43.93</v>
-      </c>
-      <c r="E373">
         <v>16814</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B374">
         <v>2022</v>
@@ -6840,15 +5721,12 @@
         <v>11011829</v>
       </c>
       <c r="D374">
-        <v>40.049999999999997</v>
-      </c>
-      <c r="E374">
         <v>4410</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B375">
         <v>2023</v>
@@ -6857,15 +5735,12 @@
         <v>36622535</v>
       </c>
       <c r="D375">
-        <v>40.21</v>
-      </c>
-      <c r="E375">
         <v>14725</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B376">
         <v>2024</v>
@@ -6874,15 +5749,12 @@
         <v>11582322</v>
       </c>
       <c r="D376">
-        <v>30.9</v>
-      </c>
-      <c r="E376">
         <v>3578</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B377">
         <v>2010</v>
@@ -6891,15 +5763,12 @@
         <v>40536964</v>
       </c>
       <c r="D377">
-        <v>27.73</v>
-      </c>
-      <c r="E377">
         <v>11240</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B378">
         <v>2011</v>
@@ -6908,15 +5777,12 @@
         <v>23230009</v>
       </c>
       <c r="D378">
-        <v>26.78</v>
-      </c>
-      <c r="E378">
         <v>6220</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B379">
         <v>2012</v>
@@ -6925,15 +5791,12 @@
         <v>43355866</v>
       </c>
       <c r="D379">
-        <v>41.45</v>
-      </c>
-      <c r="E379">
         <v>17971</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B380">
         <v>2013</v>
@@ -6942,15 +5805,12 @@
         <v>9692300</v>
       </c>
       <c r="D380">
-        <v>26.37</v>
-      </c>
-      <c r="E380">
         <v>2555</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B381">
         <v>2014</v>
@@ -6959,15 +5819,12 @@
         <v>12748352</v>
       </c>
       <c r="D381">
-        <v>24.82</v>
-      </c>
-      <c r="E381">
         <v>3164</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B382">
         <v>2015</v>
@@ -6976,15 +5833,12 @@
         <v>28772916</v>
       </c>
       <c r="D382">
-        <v>5.45</v>
-      </c>
-      <c r="E382">
         <v>1568</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B383">
         <v>2016</v>
@@ -6993,15 +5847,12 @@
         <v>15252367</v>
       </c>
       <c r="D383">
-        <v>14.17</v>
-      </c>
-      <c r="E383">
         <v>2161</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B384">
         <v>2017</v>
@@ -7010,15 +5861,12 @@
         <v>42430173</v>
       </c>
       <c r="D384">
-        <v>14.64</v>
-      </c>
-      <c r="E384">
         <v>6211</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B385">
         <v>2018</v>
@@ -7027,15 +5875,12 @@
         <v>6936446</v>
       </c>
       <c r="D385">
-        <v>22.11</v>
-      </c>
-      <c r="E385">
         <v>1533</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B386">
         <v>2019</v>
@@ -7044,15 +5889,12 @@
         <v>9557014</v>
       </c>
       <c r="D386">
-        <v>8.34</v>
-      </c>
-      <c r="E386">
         <v>797</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B387">
         <v>2020</v>
@@ -7061,15 +5903,12 @@
         <v>11742014</v>
       </c>
       <c r="D387">
-        <v>8.1</v>
-      </c>
-      <c r="E387">
         <v>951</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B388">
         <v>2021</v>
@@ -7078,15 +5917,12 @@
         <v>11941374</v>
       </c>
       <c r="D388">
-        <v>29.62</v>
-      </c>
-      <c r="E388">
         <v>3537</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B389">
         <v>2022</v>
@@ -7095,15 +5931,12 @@
         <v>3594235</v>
       </c>
       <c r="D389">
-        <v>58.8</v>
-      </c>
-      <c r="E389">
         <v>2113</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B390">
         <v>2023</v>
@@ -7112,15 +5945,12 @@
         <v>23263342</v>
       </c>
       <c r="D390">
-        <v>60.04</v>
-      </c>
-      <c r="E390">
         <v>13967</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B391">
         <v>2024</v>
@@ -7129,9 +5959,6 @@
         <v>34442384</v>
       </c>
       <c r="D391">
-        <v>54.02</v>
-      </c>
-      <c r="E391">
         <v>18605</v>
       </c>
     </row>
